--- a/Doc/数据表总览.xlsx
+++ b/Doc/数据表总览.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18052" windowHeight="8655"/>
+    <workbookView windowWidth="18052" windowHeight="8655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="关卡数据表" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">关卡数据表!$A$2:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">敌人数据表!$A$2:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">卡牌数据表!$A$3:$G$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
   <si>
     <t>关卡序号</t>
   </si>
@@ -129,6 +130,174 @@
     <t>Enemy_level</t>
   </si>
   <si>
+    <t>卡牌名称</t>
+  </si>
+  <si>
+    <t>卡牌种类</t>
+  </si>
+  <si>
+    <t>卡牌稀有度</t>
+  </si>
+  <si>
+    <t>卡牌法力值消耗上限</t>
+  </si>
+  <si>
+    <t>卡牌描述</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>用来给程序看，不写入游戏展示给玩家</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Describe</t>
+  </si>
+  <si>
+    <t>护身术</t>
+  </si>
+  <si>
+    <t>非伤害类</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>获得持续10s的护盾，每消耗1点法力值护盾可吸收的伤害增加10点。若为第一张，护盾额外吸收10点伤害。</t>
+  </si>
+  <si>
+    <t>每整数法力值影响效果，例：消耗1.5法力值获得的护盾与1法力值相同</t>
+  </si>
+  <si>
+    <t>驱鬼符</t>
+  </si>
+  <si>
+    <t>伤害类</t>
+  </si>
+  <si>
+    <t>对范围路径上的敌人造成30点物理伤害。若为第一张，额外造成30点物理伤害。</t>
+  </si>
+  <si>
+    <t>、无</t>
+  </si>
+  <si>
+    <t>火墙术</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>在范围路径上生成火焰屏障，火焰屏障会跟随玩家一起移动，屏障附近的敌人每秒受到20点法术伤害，持续6s。若为第一张，火焰屏障生效范围翻倍。</t>
+  </si>
+  <si>
+    <t>附近为0.5距离，生效翻倍后为1距离</t>
+  </si>
+  <si>
+    <t>木增术</t>
+  </si>
+  <si>
+    <t>在范围路径上产生青草区域，玩家在区域上移动速度+0.5，敌人速度-0.5，持续10s。若为第一张，额外持续5s。</t>
+  </si>
+  <si>
+    <t>水流术</t>
+  </si>
+  <si>
+    <t>推开距离3以内的所有敌人，每消耗1点法力值便推开1m。若为第一张，改为推开距离4以内的敌人。</t>
+  </si>
+  <si>
+    <t>每整数法力值影响效果</t>
+  </si>
+  <si>
+    <t>土起术</t>
+  </si>
+  <si>
+    <t>在范围路径上生成土墙，玩家和敌人均无法通过，土墙可以阻挡部分弹幕和技能。持续4s。若为第一张，额外持续4s</t>
+  </si>
+  <si>
+    <t>土墙设置为和地图边缘一个属性</t>
+  </si>
+  <si>
+    <t>金锋术</t>
+  </si>
+  <si>
+    <t>召唤一把矛，从范围路径起点开始穿刺到终点，对路径上的敌人造成180点伤害。每消耗1点法力值造成的伤害便减少30点。若为第一张，初始伤害变为240点。</t>
+  </si>
+  <si>
+    <t>矛的移动速度为5</t>
+  </si>
+  <si>
+    <t>瞬身法</t>
+  </si>
+  <si>
+    <t>在玩家下次到达路径起点/终点时，瞬间移动到路劲的终点/起点。若为第一张，额外对瞬移时路径上的敌人造成120点伤害。</t>
+  </si>
+  <si>
+    <t>起点和终点均用红色圆圈提示</t>
+  </si>
+  <si>
+    <t>雷电符</t>
+  </si>
+  <si>
+    <t>对视野内生命值最高的1个敌人造成90点伤害，每消耗1点法力值便额外重复一次。若为第一张，受到伤害的敌人周围的其他敌人也会受到30点伤害。</t>
+  </si>
+  <si>
+    <t>周围为0.5距离</t>
+  </si>
+  <si>
+    <t>祈雨符</t>
+  </si>
+  <si>
+    <t>在闭合区域内召唤一朵云，玩家在闭合区域内超过8s，则该符咒结束后恢复30%最大生命值。每消耗1点法力值，持续时间增加5s。若为第一张，先恢复10%最大生命值</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>金身符</t>
+  </si>
+  <si>
+    <t>固定消耗1点法力值。消除玩家的所有负面状态。若为第一张，接下来8s免疫所有负面状态。</t>
+  </si>
+  <si>
+    <t>有免疫状态玩家模型周围有金色边框提示</t>
+  </si>
+  <si>
+    <t>黑色莲花</t>
+  </si>
+  <si>
+    <t>罕见</t>
+  </si>
+  <si>
+    <t>在地图上随机地点召唤一朵黑色的莲花，在持续时间前触碰到黑色莲花，恢复所有法力值。每消耗1点法力值，持续时间增加3s。若为第一张，生成莲花时提示位置。</t>
+  </si>
+  <si>
+    <t>一定生成在玩家视野外，提示为箭头指向视野外的生成地点。</t>
+  </si>
+  <si>
     <t>武器类型</t>
   </si>
   <si>
@@ -153,22 +322,7 @@
     <t>攻击方式</t>
   </si>
   <si>
-    <t>Integer</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
     <t>Float</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Name</t>
   </si>
   <si>
     <t>Slot</t>
@@ -440,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -455,13 +609,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.25"/>
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +818,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -696,6 +862,30 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,7 +1013,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -835,119 +1025,119 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -981,31 +1171,70 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1548,1092 +1777,1092 @@
     <col min="7" max="7" width="13.283185840708" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" ht="39.4" spans="1:7">
-      <c r="A1" s="14" t="s">
+    <row r="1" s="25" customFormat="1" spans="1:7">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="1" ht="41.65" spans="1:7">
-      <c r="A2" s="15" t="s">
+    <row r="2" s="26" customFormat="1" ht="13.9" spans="1:7">
+      <c r="A2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A3" s="17">
+    <row r="3" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A3" s="30">
         <v>1</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="31">
         <v>40</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="32">
         <v>0</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="31">
         <v>3</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="31">
         <v>1</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="31">
         <v>5</v>
       </c>
-      <c r="G3" s="18"/>
-    </row>
-    <row r="4" s="12" customFormat="1" ht="13.85" spans="1:6">
-      <c r="A4" s="20">
+      <c r="G3" s="31"/>
+    </row>
+    <row r="4" s="25" customFormat="1" ht="13.85" spans="1:6">
+      <c r="A4" s="33">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="25">
         <v>40</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="25">
         <v>20</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="25">
         <v>2</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="25">
         <v>1</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="25">
         <v>4</v>
       </c>
     </row>
-    <row r="5" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A5" s="17">
+    <row r="5" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A5" s="30">
         <v>2</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="31">
         <v>40</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="31">
         <v>0</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="31">
         <v>3</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="31">
         <v>1</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="31">
         <v>5</v>
       </c>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" s="12" customFormat="1" ht="13.85" spans="1:6">
-      <c r="A6" s="20">
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" s="25" customFormat="1" ht="13.85" spans="1:6">
+      <c r="A6" s="33">
         <v>2</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="25">
         <v>40</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="25">
         <v>10</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="25">
         <v>2</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="25">
         <v>1</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="25">
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" s="12" customFormat="1"/>
-    <row r="9" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" s="12" customFormat="1"/>
-    <row r="11" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" s="12" customFormat="1"/>
-    <row r="13" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" s="12" customFormat="1"/>
-    <row r="15" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" s="12" customFormat="1"/>
-    <row r="17" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" s="12" customFormat="1"/>
-    <row r="19" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" s="12" customFormat="1"/>
-    <row r="21" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" s="12" customFormat="1"/>
-    <row r="23" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" s="12" customFormat="1"/>
-    <row r="25" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A25" s="17"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-    </row>
-    <row r="26" s="12" customFormat="1"/>
-    <row r="27" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A27" s="17"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" s="12" customFormat="1"/>
-    <row r="29" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A29" s="17"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" s="12" customFormat="1"/>
-    <row r="31" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A31" s="17"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" s="12" customFormat="1"/>
-    <row r="33" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-    </row>
-    <row r="34" s="12" customFormat="1"/>
-    <row r="35" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A35" s="17"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-    </row>
-    <row r="36" s="12" customFormat="1"/>
-    <row r="37" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A37" s="17"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-    </row>
-    <row r="38" s="12" customFormat="1"/>
-    <row r="39" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A39" s="17"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-    </row>
-    <row r="40" s="12" customFormat="1"/>
-    <row r="41" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A41" s="17"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-    </row>
-    <row r="42" s="12" customFormat="1"/>
-    <row r="43" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A43" s="17"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-    </row>
-    <row r="44" s="12" customFormat="1"/>
-    <row r="45" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A45" s="17"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-    </row>
-    <row r="46" s="12" customFormat="1"/>
-    <row r="47" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A47" s="17"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-    </row>
-    <row r="48" s="12" customFormat="1"/>
-    <row r="49" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A49" s="17"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-    </row>
-    <row r="50" s="12" customFormat="1"/>
-    <row r="51" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A51" s="17"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-    </row>
-    <row r="52" s="12" customFormat="1"/>
-    <row r="53" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A53" s="17"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-    </row>
-    <row r="54" s="12" customFormat="1"/>
-    <row r="55" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A55" s="17"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-    </row>
-    <row r="56" s="12" customFormat="1"/>
-    <row r="57" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A57" s="17"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-    </row>
-    <row r="58" s="12" customFormat="1"/>
-    <row r="59" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A59" s="17"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-    </row>
-    <row r="60" s="12" customFormat="1"/>
-    <row r="61" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A61" s="17"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-    </row>
-    <row r="62" s="12" customFormat="1"/>
-    <row r="63" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A63" s="17"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-    </row>
-    <row r="64" s="12" customFormat="1"/>
-    <row r="65" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A65" s="17"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-    </row>
-    <row r="66" s="12" customFormat="1"/>
-    <row r="67" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A67" s="17"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-    </row>
-    <row r="68" s="12" customFormat="1"/>
-    <row r="69" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A69" s="17"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-    </row>
-    <row r="70" s="12" customFormat="1"/>
-    <row r="71" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A71" s="17"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-    </row>
-    <row r="72" s="12" customFormat="1"/>
-    <row r="73" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A73" s="17"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-    </row>
-    <row r="74" s="12" customFormat="1"/>
-    <row r="75" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A75" s="17"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-    </row>
-    <row r="76" s="12" customFormat="1"/>
-    <row r="77" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A77" s="17"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-    </row>
-    <row r="78" s="12" customFormat="1"/>
-    <row r="79" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A79" s="17"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-    </row>
-    <row r="80" s="12" customFormat="1"/>
-    <row r="81" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A81" s="17"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-    </row>
-    <row r="82" s="12" customFormat="1"/>
-    <row r="83" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A83" s="17"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
-    </row>
-    <row r="84" s="12" customFormat="1"/>
-    <row r="85" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A85" s="17"/>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="18"/>
-    </row>
-    <row r="86" s="12" customFormat="1"/>
-    <row r="87" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A87" s="17"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-    </row>
-    <row r="88" s="12" customFormat="1"/>
-    <row r="89" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A89" s="17"/>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-    </row>
-    <row r="90" s="12" customFormat="1"/>
-    <row r="91" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A91" s="17"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-    </row>
-    <row r="92" s="12" customFormat="1"/>
-    <row r="93" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A93" s="17"/>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-    </row>
-    <row r="94" s="12" customFormat="1"/>
-    <row r="95" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A95" s="17"/>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
-    </row>
-    <row r="96" s="12" customFormat="1"/>
-    <row r="97" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A97" s="17"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-    </row>
-    <row r="98" s="12" customFormat="1"/>
-    <row r="99" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A99" s="17"/>
-      <c r="B99" s="18"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
-      <c r="F99" s="18"/>
-      <c r="G99" s="18"/>
-    </row>
-    <row r="100" s="12" customFormat="1"/>
-    <row r="101" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A101" s="17"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
-      <c r="F101" s="18"/>
-      <c r="G101" s="18"/>
-    </row>
-    <row r="102" s="12" customFormat="1"/>
-    <row r="103" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A103" s="17"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="18"/>
-      <c r="E103" s="18"/>
-      <c r="F103" s="18"/>
-      <c r="G103" s="18"/>
-    </row>
-    <row r="104" s="12" customFormat="1"/>
-    <row r="105" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A105" s="17"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
-      <c r="G105" s="18"/>
-    </row>
-    <row r="106" s="12" customFormat="1"/>
-    <row r="107" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A107" s="17"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="18"/>
-      <c r="D107" s="18"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="18"/>
-      <c r="G107" s="18"/>
-    </row>
-    <row r="108" s="12" customFormat="1"/>
-    <row r="109" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A109" s="17"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-    </row>
-    <row r="110" s="12" customFormat="1"/>
-    <row r="111" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A111" s="17"/>
-      <c r="B111" s="18"/>
-      <c r="C111" s="18"/>
-      <c r="D111" s="18"/>
-      <c r="E111" s="18"/>
-      <c r="F111" s="18"/>
-      <c r="G111" s="18"/>
-    </row>
-    <row r="112" s="12" customFormat="1"/>
-    <row r="113" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A113" s="17"/>
-      <c r="B113" s="18"/>
-      <c r="C113" s="18"/>
-      <c r="D113" s="18"/>
-      <c r="E113" s="18"/>
-      <c r="F113" s="18"/>
-      <c r="G113" s="18"/>
-    </row>
-    <row r="114" s="12" customFormat="1"/>
-    <row r="115" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A115" s="17"/>
-      <c r="B115" s="18"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="18"/>
-      <c r="G115" s="18"/>
-    </row>
-    <row r="116" s="12" customFormat="1"/>
-    <row r="117" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A117" s="17"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="18"/>
-      <c r="G117" s="18"/>
-    </row>
-    <row r="118" s="12" customFormat="1"/>
-    <row r="119" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A119" s="17"/>
-      <c r="B119" s="18"/>
-      <c r="C119" s="18"/>
-      <c r="D119" s="18"/>
-      <c r="E119" s="18"/>
-      <c r="F119" s="18"/>
-      <c r="G119" s="18"/>
-    </row>
-    <row r="120" s="12" customFormat="1"/>
-    <row r="121" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A121" s="17"/>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="18"/>
-      <c r="E121" s="18"/>
-      <c r="F121" s="18"/>
-      <c r="G121" s="18"/>
-    </row>
-    <row r="122" s="12" customFormat="1"/>
-    <row r="123" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A123" s="17"/>
-      <c r="B123" s="18"/>
-      <c r="C123" s="18"/>
-      <c r="D123" s="18"/>
-      <c r="E123" s="18"/>
-      <c r="F123" s="18"/>
-      <c r="G123" s="18"/>
-    </row>
-    <row r="124" s="12" customFormat="1"/>
-    <row r="125" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A125" s="17"/>
-      <c r="B125" s="18"/>
-      <c r="C125" s="18"/>
-      <c r="D125" s="18"/>
-      <c r="E125" s="18"/>
-      <c r="F125" s="18"/>
-      <c r="G125" s="18"/>
-    </row>
-    <row r="126" s="12" customFormat="1"/>
-    <row r="127" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A127" s="17"/>
-      <c r="B127" s="18"/>
-      <c r="C127" s="18"/>
-      <c r="D127" s="18"/>
-      <c r="E127" s="18"/>
-      <c r="F127" s="18"/>
-      <c r="G127" s="18"/>
-    </row>
-    <row r="128" s="12" customFormat="1"/>
-    <row r="129" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A129" s="17"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
-      <c r="F129" s="18"/>
-      <c r="G129" s="18"/>
-    </row>
-    <row r="130" s="12" customFormat="1"/>
-    <row r="131" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A131" s="17"/>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-    </row>
-    <row r="132" s="12" customFormat="1"/>
-    <row r="133" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A133" s="17"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="18"/>
-    </row>
-    <row r="134" s="12" customFormat="1"/>
-    <row r="135" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A135" s="17"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="18"/>
-    </row>
-    <row r="136" s="12" customFormat="1"/>
-    <row r="137" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A137" s="17"/>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="18"/>
-    </row>
-    <row r="138" s="12" customFormat="1"/>
-    <row r="139" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A139" s="17"/>
-      <c r="B139" s="18"/>
-      <c r="C139" s="18"/>
-      <c r="D139" s="18"/>
-      <c r="E139" s="18"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="18"/>
-    </row>
-    <row r="140" s="12" customFormat="1"/>
-    <row r="141" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A141" s="17"/>
-      <c r="B141" s="18"/>
-      <c r="C141" s="18"/>
-      <c r="D141" s="18"/>
-      <c r="E141" s="18"/>
-      <c r="F141" s="18"/>
-      <c r="G141" s="18"/>
-    </row>
-    <row r="142" s="12" customFormat="1"/>
-    <row r="143" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A143" s="17"/>
-      <c r="B143" s="18"/>
-      <c r="C143" s="18"/>
-      <c r="D143" s="18"/>
-      <c r="E143" s="18"/>
-      <c r="F143" s="18"/>
-      <c r="G143" s="18"/>
-    </row>
-    <row r="144" s="12" customFormat="1"/>
-    <row r="145" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A145" s="17"/>
-      <c r="B145" s="18"/>
-      <c r="C145" s="18"/>
-      <c r="D145" s="18"/>
-      <c r="E145" s="18"/>
-      <c r="F145" s="18"/>
-      <c r="G145" s="18"/>
-    </row>
-    <row r="146" s="12" customFormat="1"/>
-    <row r="147" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A147" s="17"/>
-      <c r="B147" s="18"/>
-      <c r="C147" s="18"/>
-      <c r="D147" s="18"/>
-      <c r="E147" s="18"/>
-      <c r="F147" s="18"/>
-      <c r="G147" s="18"/>
-    </row>
-    <row r="148" s="12" customFormat="1"/>
-    <row r="149" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A149" s="17"/>
-      <c r="B149" s="18"/>
-      <c r="C149" s="18"/>
-      <c r="D149" s="18"/>
-      <c r="E149" s="18"/>
-      <c r="F149" s="18"/>
-      <c r="G149" s="18"/>
-    </row>
-    <row r="150" s="12" customFormat="1"/>
-    <row r="151" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A151" s="17"/>
-      <c r="B151" s="18"/>
-      <c r="C151" s="18"/>
-      <c r="D151" s="18"/>
-      <c r="E151" s="18"/>
-      <c r="F151" s="18"/>
-      <c r="G151" s="18"/>
-    </row>
-    <row r="152" s="12" customFormat="1"/>
-    <row r="153" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A153" s="17"/>
-      <c r="B153" s="18"/>
-      <c r="C153" s="18"/>
-      <c r="D153" s="18"/>
-      <c r="E153" s="18"/>
-      <c r="F153" s="18"/>
-      <c r="G153" s="18"/>
-    </row>
-    <row r="154" s="12" customFormat="1"/>
-    <row r="155" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A155" s="17"/>
-      <c r="B155" s="18"/>
-      <c r="C155" s="18"/>
-      <c r="D155" s="18"/>
-      <c r="E155" s="18"/>
-      <c r="F155" s="18"/>
-      <c r="G155" s="18"/>
-    </row>
-    <row r="156" s="12" customFormat="1"/>
-    <row r="157" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A157" s="17"/>
-      <c r="B157" s="18"/>
-      <c r="C157" s="18"/>
-      <c r="D157" s="18"/>
-      <c r="E157" s="18"/>
-      <c r="F157" s="18"/>
-      <c r="G157" s="18"/>
-    </row>
-    <row r="158" s="12" customFormat="1"/>
-    <row r="159" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A159" s="17"/>
-      <c r="B159" s="18"/>
-      <c r="C159" s="18"/>
-      <c r="D159" s="18"/>
-      <c r="E159" s="18"/>
-      <c r="F159" s="18"/>
-      <c r="G159" s="18"/>
-    </row>
-    <row r="160" s="12" customFormat="1"/>
-    <row r="161" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A161" s="17"/>
-      <c r="B161" s="18"/>
-      <c r="C161" s="18"/>
-      <c r="D161" s="18"/>
-      <c r="E161" s="18"/>
-      <c r="F161" s="18"/>
-      <c r="G161" s="18"/>
-    </row>
-    <row r="162" s="12" customFormat="1"/>
-    <row r="163" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A163" s="17"/>
-      <c r="B163" s="18"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="18"/>
-      <c r="E163" s="18"/>
-      <c r="F163" s="18"/>
-      <c r="G163" s="18"/>
-    </row>
-    <row r="164" s="12" customFormat="1"/>
-    <row r="165" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A165" s="17"/>
-      <c r="B165" s="18"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="18"/>
-      <c r="E165" s="18"/>
-      <c r="F165" s="18"/>
-      <c r="G165" s="18"/>
-    </row>
-    <row r="166" s="12" customFormat="1"/>
-    <row r="167" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A167" s="17"/>
-      <c r="B167" s="18"/>
-      <c r="C167" s="18"/>
-      <c r="D167" s="18"/>
-      <c r="E167" s="18"/>
-      <c r="F167" s="18"/>
-      <c r="G167" s="18"/>
-    </row>
-    <row r="168" s="12" customFormat="1"/>
-    <row r="169" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A169" s="17"/>
-      <c r="B169" s="18"/>
-      <c r="C169" s="18"/>
-      <c r="D169" s="18"/>
-      <c r="E169" s="18"/>
-      <c r="F169" s="18"/>
-      <c r="G169" s="18"/>
-    </row>
-    <row r="170" s="12" customFormat="1"/>
-    <row r="171" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A171" s="17"/>
-      <c r="B171" s="18"/>
-      <c r="C171" s="18"/>
-      <c r="D171" s="18"/>
-      <c r="E171" s="18"/>
-      <c r="F171" s="18"/>
-      <c r="G171" s="18"/>
-    </row>
-    <row r="172" s="12" customFormat="1"/>
-    <row r="173" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A173" s="17"/>
-      <c r="B173" s="18"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="18"/>
-      <c r="E173" s="18"/>
-      <c r="F173" s="18"/>
-      <c r="G173" s="18"/>
-    </row>
-    <row r="174" s="12" customFormat="1"/>
-    <row r="175" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A175" s="17"/>
-      <c r="B175" s="18"/>
-      <c r="C175" s="18"/>
-      <c r="D175" s="18"/>
-      <c r="E175" s="18"/>
-      <c r="F175" s="18"/>
-      <c r="G175" s="18"/>
-    </row>
-    <row r="176" s="12" customFormat="1"/>
-    <row r="177" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A177" s="17"/>
-      <c r="B177" s="18"/>
-      <c r="C177" s="18"/>
-      <c r="D177" s="18"/>
-      <c r="E177" s="18"/>
-      <c r="F177" s="18"/>
-      <c r="G177" s="18"/>
-    </row>
-    <row r="178" s="12" customFormat="1"/>
-    <row r="179" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A179" s="17"/>
-      <c r="B179" s="18"/>
-      <c r="C179" s="18"/>
-      <c r="D179" s="18"/>
-      <c r="E179" s="18"/>
-      <c r="F179" s="18"/>
-      <c r="G179" s="18"/>
-    </row>
-    <row r="180" s="12" customFormat="1"/>
-    <row r="181" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A181" s="17"/>
-      <c r="B181" s="18"/>
-      <c r="C181" s="18"/>
-      <c r="D181" s="18"/>
-      <c r="E181" s="18"/>
-      <c r="F181" s="18"/>
-      <c r="G181" s="18"/>
-    </row>
-    <row r="182" s="12" customFormat="1"/>
-    <row r="183" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A183" s="17"/>
-      <c r="B183" s="18"/>
-      <c r="C183" s="18"/>
-      <c r="D183" s="18"/>
-      <c r="E183" s="18"/>
-      <c r="F183" s="18"/>
-      <c r="G183" s="18"/>
-    </row>
-    <row r="184" s="12" customFormat="1"/>
-    <row r="185" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A185" s="17"/>
-      <c r="B185" s="18"/>
-      <c r="C185" s="18"/>
-      <c r="D185" s="18"/>
-      <c r="E185" s="18"/>
-      <c r="F185" s="18"/>
-      <c r="G185" s="18"/>
-    </row>
-    <row r="186" s="12" customFormat="1"/>
-    <row r="187" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A187" s="17"/>
-      <c r="B187" s="18"/>
-      <c r="C187" s="18"/>
-      <c r="D187" s="18"/>
-      <c r="E187" s="18"/>
-      <c r="F187" s="18"/>
-      <c r="G187" s="18"/>
-    </row>
-    <row r="188" s="12" customFormat="1"/>
-    <row r="189" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A189" s="17"/>
-      <c r="B189" s="18"/>
-      <c r="C189" s="18"/>
-      <c r="D189" s="18"/>
-      <c r="E189" s="18"/>
-      <c r="F189" s="18"/>
-      <c r="G189" s="18"/>
-    </row>
-    <row r="190" s="12" customFormat="1"/>
-    <row r="191" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A191" s="17"/>
-      <c r="B191" s="18"/>
-      <c r="C191" s="18"/>
-      <c r="D191" s="18"/>
-      <c r="E191" s="18"/>
-      <c r="F191" s="18"/>
-      <c r="G191" s="18"/>
-    </row>
-    <row r="192" s="12" customFormat="1"/>
-    <row r="193" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A193" s="17"/>
-      <c r="B193" s="18"/>
-      <c r="C193" s="18"/>
-      <c r="D193" s="18"/>
-      <c r="E193" s="18"/>
-      <c r="F193" s="18"/>
-      <c r="G193" s="18"/>
-    </row>
-    <row r="194" s="12" customFormat="1"/>
-    <row r="195" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A195" s="17"/>
-      <c r="B195" s="18"/>
-      <c r="C195" s="18"/>
-      <c r="D195" s="18"/>
-      <c r="E195" s="18"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="18"/>
-    </row>
-    <row r="196" s="12" customFormat="1"/>
-    <row r="197" s="12" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A197" s="17"/>
-      <c r="B197" s="18"/>
-      <c r="C197" s="18"/>
-      <c r="D197" s="18"/>
-      <c r="E197" s="18"/>
-      <c r="F197" s="18"/>
-      <c r="G197" s="18"/>
+    <row r="7" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+    </row>
+    <row r="8" s="25" customFormat="1"/>
+    <row r="9" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" s="25" customFormat="1"/>
+    <row r="11" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+    </row>
+    <row r="12" s="25" customFormat="1"/>
+    <row r="13" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+    </row>
+    <row r="14" s="25" customFormat="1"/>
+    <row r="15" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+    </row>
+    <row r="16" s="25" customFormat="1"/>
+    <row r="17" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A17" s="30"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+    </row>
+    <row r="18" s="25" customFormat="1"/>
+    <row r="19" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+    </row>
+    <row r="20" s="25" customFormat="1"/>
+    <row r="21" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+    </row>
+    <row r="22" s="25" customFormat="1"/>
+    <row r="23" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+    </row>
+    <row r="24" s="25" customFormat="1"/>
+    <row r="25" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A25" s="30"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+    </row>
+    <row r="26" s="25" customFormat="1"/>
+    <row r="27" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A27" s="30"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+    </row>
+    <row r="28" s="25" customFormat="1"/>
+    <row r="29" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+    </row>
+    <row r="30" s="25" customFormat="1"/>
+    <row r="31" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+    </row>
+    <row r="32" s="25" customFormat="1"/>
+    <row r="33" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+    </row>
+    <row r="34" s="25" customFormat="1"/>
+    <row r="35" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A35" s="30"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+    </row>
+    <row r="36" s="25" customFormat="1"/>
+    <row r="37" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+    </row>
+    <row r="38" s="25" customFormat="1"/>
+    <row r="39" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A39" s="30"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+    </row>
+    <row r="40" s="25" customFormat="1"/>
+    <row r="41" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A41" s="30"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+    </row>
+    <row r="42" s="25" customFormat="1"/>
+    <row r="43" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+    </row>
+    <row r="44" s="25" customFormat="1"/>
+    <row r="45" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A45" s="30"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+    </row>
+    <row r="46" s="25" customFormat="1"/>
+    <row r="47" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+    </row>
+    <row r="48" s="25" customFormat="1"/>
+    <row r="49" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+    </row>
+    <row r="50" s="25" customFormat="1"/>
+    <row r="51" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A51" s="30"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+    </row>
+    <row r="52" s="25" customFormat="1"/>
+    <row r="53" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A53" s="30"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+    </row>
+    <row r="54" s="25" customFormat="1"/>
+    <row r="55" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+    </row>
+    <row r="56" s="25" customFormat="1"/>
+    <row r="57" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+    </row>
+    <row r="58" s="25" customFormat="1"/>
+    <row r="59" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A59" s="30"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
+    </row>
+    <row r="60" s="25" customFormat="1"/>
+    <row r="61" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+    </row>
+    <row r="62" s="25" customFormat="1"/>
+    <row r="63" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A63" s="30"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31"/>
+    </row>
+    <row r="64" s="25" customFormat="1"/>
+    <row r="65" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A65" s="30"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+    </row>
+    <row r="66" s="25" customFormat="1"/>
+    <row r="67" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A67" s="30"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+    </row>
+    <row r="68" s="25" customFormat="1"/>
+    <row r="69" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A69" s="30"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+    </row>
+    <row r="70" s="25" customFormat="1"/>
+    <row r="71" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A71" s="30"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+    </row>
+    <row r="72" s="25" customFormat="1"/>
+    <row r="73" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A73" s="30"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+    </row>
+    <row r="74" s="25" customFormat="1"/>
+    <row r="75" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+    </row>
+    <row r="76" s="25" customFormat="1"/>
+    <row r="77" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A77" s="30"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+    </row>
+    <row r="78" s="25" customFormat="1"/>
+    <row r="79" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A79" s="30"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+    </row>
+    <row r="80" s="25" customFormat="1"/>
+    <row r="81" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A81" s="30"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+    </row>
+    <row r="82" s="25" customFormat="1"/>
+    <row r="83" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A83" s="30"/>
+      <c r="B83" s="31"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
+    </row>
+    <row r="84" s="25" customFormat="1"/>
+    <row r="85" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A85" s="30"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
+      <c r="D85" s="31"/>
+      <c r="E85" s="31"/>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31"/>
+    </row>
+    <row r="86" s="25" customFormat="1"/>
+    <row r="87" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
+    </row>
+    <row r="88" s="25" customFormat="1"/>
+    <row r="89" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A89" s="30"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="31"/>
+      <c r="E89" s="31"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="31"/>
+    </row>
+    <row r="90" s="25" customFormat="1"/>
+    <row r="91" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A91" s="30"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="31"/>
+      <c r="D91" s="31"/>
+      <c r="E91" s="31"/>
+      <c r="F91" s="31"/>
+      <c r="G91" s="31"/>
+    </row>
+    <row r="92" s="25" customFormat="1"/>
+    <row r="93" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A93" s="30"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="31"/>
+      <c r="D93" s="31"/>
+      <c r="E93" s="31"/>
+      <c r="F93" s="31"/>
+      <c r="G93" s="31"/>
+    </row>
+    <row r="94" s="25" customFormat="1"/>
+    <row r="95" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A95" s="30"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="31"/>
+      <c r="D95" s="31"/>
+      <c r="E95" s="31"/>
+      <c r="F95" s="31"/>
+      <c r="G95" s="31"/>
+    </row>
+    <row r="96" s="25" customFormat="1"/>
+    <row r="97" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A97" s="30"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="31"/>
+      <c r="D97" s="31"/>
+      <c r="E97" s="31"/>
+      <c r="F97" s="31"/>
+      <c r="G97" s="31"/>
+    </row>
+    <row r="98" s="25" customFormat="1"/>
+    <row r="99" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A99" s="30"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
+      <c r="D99" s="31"/>
+      <c r="E99" s="31"/>
+      <c r="F99" s="31"/>
+      <c r="G99" s="31"/>
+    </row>
+    <row r="100" s="25" customFormat="1"/>
+    <row r="101" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A101" s="30"/>
+      <c r="B101" s="31"/>
+      <c r="C101" s="31"/>
+      <c r="D101" s="31"/>
+      <c r="E101" s="31"/>
+      <c r="F101" s="31"/>
+      <c r="G101" s="31"/>
+    </row>
+    <row r="102" s="25" customFormat="1"/>
+    <row r="103" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A103" s="30"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="31"/>
+      <c r="D103" s="31"/>
+      <c r="E103" s="31"/>
+      <c r="F103" s="31"/>
+      <c r="G103" s="31"/>
+    </row>
+    <row r="104" s="25" customFormat="1"/>
+    <row r="105" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A105" s="30"/>
+      <c r="B105" s="31"/>
+      <c r="C105" s="31"/>
+      <c r="D105" s="31"/>
+      <c r="E105" s="31"/>
+      <c r="F105" s="31"/>
+      <c r="G105" s="31"/>
+    </row>
+    <row r="106" s="25" customFormat="1"/>
+    <row r="107" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A107" s="30"/>
+      <c r="B107" s="31"/>
+      <c r="C107" s="31"/>
+      <c r="D107" s="31"/>
+      <c r="E107" s="31"/>
+      <c r="F107" s="31"/>
+      <c r="G107" s="31"/>
+    </row>
+    <row r="108" s="25" customFormat="1"/>
+    <row r="109" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A109" s="30"/>
+      <c r="B109" s="31"/>
+      <c r="C109" s="31"/>
+      <c r="D109" s="31"/>
+      <c r="E109" s="31"/>
+      <c r="F109" s="31"/>
+      <c r="G109" s="31"/>
+    </row>
+    <row r="110" s="25" customFormat="1"/>
+    <row r="111" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A111" s="30"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="31"/>
+      <c r="D111" s="31"/>
+      <c r="E111" s="31"/>
+      <c r="F111" s="31"/>
+      <c r="G111" s="31"/>
+    </row>
+    <row r="112" s="25" customFormat="1"/>
+    <row r="113" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A113" s="30"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="31"/>
+      <c r="D113" s="31"/>
+      <c r="E113" s="31"/>
+      <c r="F113" s="31"/>
+      <c r="G113" s="31"/>
+    </row>
+    <row r="114" s="25" customFormat="1"/>
+    <row r="115" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A115" s="30"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="31"/>
+      <c r="D115" s="31"/>
+      <c r="E115" s="31"/>
+      <c r="F115" s="31"/>
+      <c r="G115" s="31"/>
+    </row>
+    <row r="116" s="25" customFormat="1"/>
+    <row r="117" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A117" s="30"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="31"/>
+      <c r="D117" s="31"/>
+      <c r="E117" s="31"/>
+      <c r="F117" s="31"/>
+      <c r="G117" s="31"/>
+    </row>
+    <row r="118" s="25" customFormat="1"/>
+    <row r="119" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A119" s="30"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="31"/>
+      <c r="D119" s="31"/>
+      <c r="E119" s="31"/>
+      <c r="F119" s="31"/>
+      <c r="G119" s="31"/>
+    </row>
+    <row r="120" s="25" customFormat="1"/>
+    <row r="121" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A121" s="30"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="31"/>
+      <c r="D121" s="31"/>
+      <c r="E121" s="31"/>
+      <c r="F121" s="31"/>
+      <c r="G121" s="31"/>
+    </row>
+    <row r="122" s="25" customFormat="1"/>
+    <row r="123" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A123" s="30"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="31"/>
+      <c r="D123" s="31"/>
+      <c r="E123" s="31"/>
+      <c r="F123" s="31"/>
+      <c r="G123" s="31"/>
+    </row>
+    <row r="124" s="25" customFormat="1"/>
+    <row r="125" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A125" s="30"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="31"/>
+      <c r="D125" s="31"/>
+      <c r="E125" s="31"/>
+      <c r="F125" s="31"/>
+      <c r="G125" s="31"/>
+    </row>
+    <row r="126" s="25" customFormat="1"/>
+    <row r="127" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A127" s="30"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="31"/>
+      <c r="D127" s="31"/>
+      <c r="E127" s="31"/>
+      <c r="F127" s="31"/>
+      <c r="G127" s="31"/>
+    </row>
+    <row r="128" s="25" customFormat="1"/>
+    <row r="129" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A129" s="30"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="31"/>
+      <c r="D129" s="31"/>
+      <c r="E129" s="31"/>
+      <c r="F129" s="31"/>
+      <c r="G129" s="31"/>
+    </row>
+    <row r="130" s="25" customFormat="1"/>
+    <row r="131" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A131" s="30"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="31"/>
+      <c r="D131" s="31"/>
+      <c r="E131" s="31"/>
+      <c r="F131" s="31"/>
+      <c r="G131" s="31"/>
+    </row>
+    <row r="132" s="25" customFormat="1"/>
+    <row r="133" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A133" s="30"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="31"/>
+      <c r="D133" s="31"/>
+      <c r="E133" s="31"/>
+      <c r="F133" s="31"/>
+      <c r="G133" s="31"/>
+    </row>
+    <row r="134" s="25" customFormat="1"/>
+    <row r="135" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A135" s="30"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="31"/>
+      <c r="D135" s="31"/>
+      <c r="E135" s="31"/>
+      <c r="F135" s="31"/>
+      <c r="G135" s="31"/>
+    </row>
+    <row r="136" s="25" customFormat="1"/>
+    <row r="137" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A137" s="30"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="31"/>
+      <c r="D137" s="31"/>
+      <c r="E137" s="31"/>
+      <c r="F137" s="31"/>
+      <c r="G137" s="31"/>
+    </row>
+    <row r="138" s="25" customFormat="1"/>
+    <row r="139" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A139" s="30"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="31"/>
+      <c r="D139" s="31"/>
+      <c r="E139" s="31"/>
+      <c r="F139" s="31"/>
+      <c r="G139" s="31"/>
+    </row>
+    <row r="140" s="25" customFormat="1"/>
+    <row r="141" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A141" s="30"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="31"/>
+      <c r="D141" s="31"/>
+      <c r="E141" s="31"/>
+      <c r="F141" s="31"/>
+      <c r="G141" s="31"/>
+    </row>
+    <row r="142" s="25" customFormat="1"/>
+    <row r="143" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A143" s="30"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="31"/>
+      <c r="D143" s="31"/>
+      <c r="E143" s="31"/>
+      <c r="F143" s="31"/>
+      <c r="G143" s="31"/>
+    </row>
+    <row r="144" s="25" customFormat="1"/>
+    <row r="145" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A145" s="30"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="31"/>
+      <c r="D145" s="31"/>
+      <c r="E145" s="31"/>
+      <c r="F145" s="31"/>
+      <c r="G145" s="31"/>
+    </row>
+    <row r="146" s="25" customFormat="1"/>
+    <row r="147" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A147" s="30"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="31"/>
+      <c r="D147" s="31"/>
+      <c r="E147" s="31"/>
+      <c r="F147" s="31"/>
+      <c r="G147" s="31"/>
+    </row>
+    <row r="148" s="25" customFormat="1"/>
+    <row r="149" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A149" s="30"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="31"/>
+      <c r="D149" s="31"/>
+      <c r="E149" s="31"/>
+      <c r="F149" s="31"/>
+      <c r="G149" s="31"/>
+    </row>
+    <row r="150" s="25" customFormat="1"/>
+    <row r="151" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A151" s="30"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="31"/>
+      <c r="D151" s="31"/>
+      <c r="E151" s="31"/>
+      <c r="F151" s="31"/>
+      <c r="G151" s="31"/>
+    </row>
+    <row r="152" s="25" customFormat="1"/>
+    <row r="153" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A153" s="30"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="31"/>
+      <c r="D153" s="31"/>
+      <c r="E153" s="31"/>
+      <c r="F153" s="31"/>
+      <c r="G153" s="31"/>
+    </row>
+    <row r="154" s="25" customFormat="1"/>
+    <row r="155" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A155" s="30"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="31"/>
+      <c r="D155" s="31"/>
+      <c r="E155" s="31"/>
+      <c r="F155" s="31"/>
+      <c r="G155" s="31"/>
+    </row>
+    <row r="156" s="25" customFormat="1"/>
+    <row r="157" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A157" s="30"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="31"/>
+      <c r="D157" s="31"/>
+      <c r="E157" s="31"/>
+      <c r="F157" s="31"/>
+      <c r="G157" s="31"/>
+    </row>
+    <row r="158" s="25" customFormat="1"/>
+    <row r="159" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A159" s="30"/>
+      <c r="B159" s="31"/>
+      <c r="C159" s="31"/>
+      <c r="D159" s="31"/>
+      <c r="E159" s="31"/>
+      <c r="F159" s="31"/>
+      <c r="G159" s="31"/>
+    </row>
+    <row r="160" s="25" customFormat="1"/>
+    <row r="161" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A161" s="30"/>
+      <c r="B161" s="31"/>
+      <c r="C161" s="31"/>
+      <c r="D161" s="31"/>
+      <c r="E161" s="31"/>
+      <c r="F161" s="31"/>
+      <c r="G161" s="31"/>
+    </row>
+    <row r="162" s="25" customFormat="1"/>
+    <row r="163" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A163" s="30"/>
+      <c r="B163" s="31"/>
+      <c r="C163" s="31"/>
+      <c r="D163" s="31"/>
+      <c r="E163" s="31"/>
+      <c r="F163" s="31"/>
+      <c r="G163" s="31"/>
+    </row>
+    <row r="164" s="25" customFormat="1"/>
+    <row r="165" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A165" s="30"/>
+      <c r="B165" s="31"/>
+      <c r="C165" s="31"/>
+      <c r="D165" s="31"/>
+      <c r="E165" s="31"/>
+      <c r="F165" s="31"/>
+      <c r="G165" s="31"/>
+    </row>
+    <row r="166" s="25" customFormat="1"/>
+    <row r="167" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A167" s="30"/>
+      <c r="B167" s="31"/>
+      <c r="C167" s="31"/>
+      <c r="D167" s="31"/>
+      <c r="E167" s="31"/>
+      <c r="F167" s="31"/>
+      <c r="G167" s="31"/>
+    </row>
+    <row r="168" s="25" customFormat="1"/>
+    <row r="169" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A169" s="30"/>
+      <c r="B169" s="31"/>
+      <c r="C169" s="31"/>
+      <c r="D169" s="31"/>
+      <c r="E169" s="31"/>
+      <c r="F169" s="31"/>
+      <c r="G169" s="31"/>
+    </row>
+    <row r="170" s="25" customFormat="1"/>
+    <row r="171" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A171" s="30"/>
+      <c r="B171" s="31"/>
+      <c r="C171" s="31"/>
+      <c r="D171" s="31"/>
+      <c r="E171" s="31"/>
+      <c r="F171" s="31"/>
+      <c r="G171" s="31"/>
+    </row>
+    <row r="172" s="25" customFormat="1"/>
+    <row r="173" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A173" s="30"/>
+      <c r="B173" s="31"/>
+      <c r="C173" s="31"/>
+      <c r="D173" s="31"/>
+      <c r="E173" s="31"/>
+      <c r="F173" s="31"/>
+      <c r="G173" s="31"/>
+    </row>
+    <row r="174" s="25" customFormat="1"/>
+    <row r="175" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A175" s="30"/>
+      <c r="B175" s="31"/>
+      <c r="C175" s="31"/>
+      <c r="D175" s="31"/>
+      <c r="E175" s="31"/>
+      <c r="F175" s="31"/>
+      <c r="G175" s="31"/>
+    </row>
+    <row r="176" s="25" customFormat="1"/>
+    <row r="177" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A177" s="30"/>
+      <c r="B177" s="31"/>
+      <c r="C177" s="31"/>
+      <c r="D177" s="31"/>
+      <c r="E177" s="31"/>
+      <c r="F177" s="31"/>
+      <c r="G177" s="31"/>
+    </row>
+    <row r="178" s="25" customFormat="1"/>
+    <row r="179" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A179" s="30"/>
+      <c r="B179" s="31"/>
+      <c r="C179" s="31"/>
+      <c r="D179" s="31"/>
+      <c r="E179" s="31"/>
+      <c r="F179" s="31"/>
+      <c r="G179" s="31"/>
+    </row>
+    <row r="180" s="25" customFormat="1"/>
+    <row r="181" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A181" s="30"/>
+      <c r="B181" s="31"/>
+      <c r="C181" s="31"/>
+      <c r="D181" s="31"/>
+      <c r="E181" s="31"/>
+      <c r="F181" s="31"/>
+      <c r="G181" s="31"/>
+    </row>
+    <row r="182" s="25" customFormat="1"/>
+    <row r="183" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A183" s="30"/>
+      <c r="B183" s="31"/>
+      <c r="C183" s="31"/>
+      <c r="D183" s="31"/>
+      <c r="E183" s="31"/>
+      <c r="F183" s="31"/>
+      <c r="G183" s="31"/>
+    </row>
+    <row r="184" s="25" customFormat="1"/>
+    <row r="185" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A185" s="30"/>
+      <c r="B185" s="31"/>
+      <c r="C185" s="31"/>
+      <c r="D185" s="31"/>
+      <c r="E185" s="31"/>
+      <c r="F185" s="31"/>
+      <c r="G185" s="31"/>
+    </row>
+    <row r="186" s="25" customFormat="1"/>
+    <row r="187" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A187" s="30"/>
+      <c r="B187" s="31"/>
+      <c r="C187" s="31"/>
+      <c r="D187" s="31"/>
+      <c r="E187" s="31"/>
+      <c r="F187" s="31"/>
+      <c r="G187" s="31"/>
+    </row>
+    <row r="188" s="25" customFormat="1"/>
+    <row r="189" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A189" s="30"/>
+      <c r="B189" s="31"/>
+      <c r="C189" s="31"/>
+      <c r="D189" s="31"/>
+      <c r="E189" s="31"/>
+      <c r="F189" s="31"/>
+      <c r="G189" s="31"/>
+    </row>
+    <row r="190" s="25" customFormat="1"/>
+    <row r="191" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A191" s="30"/>
+      <c r="B191" s="31"/>
+      <c r="C191" s="31"/>
+      <c r="D191" s="31"/>
+      <c r="E191" s="31"/>
+      <c r="F191" s="31"/>
+      <c r="G191" s="31"/>
+    </row>
+    <row r="192" s="25" customFormat="1"/>
+    <row r="193" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A193" s="30"/>
+      <c r="B193" s="31"/>
+      <c r="C193" s="31"/>
+      <c r="D193" s="31"/>
+      <c r="E193" s="31"/>
+      <c r="F193" s="31"/>
+      <c r="G193" s="31"/>
+    </row>
+    <row r="194" s="25" customFormat="1"/>
+    <row r="195" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A195" s="30"/>
+      <c r="B195" s="31"/>
+      <c r="C195" s="31"/>
+      <c r="D195" s="31"/>
+      <c r="E195" s="31"/>
+      <c r="F195" s="31"/>
+      <c r="G195" s="31"/>
+    </row>
+    <row r="196" s="25" customFormat="1"/>
+    <row r="197" s="25" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A197" s="30"/>
+      <c r="B197" s="31"/>
+      <c r="C197" s="31"/>
+      <c r="D197" s="31"/>
+      <c r="E197" s="31"/>
+      <c r="F197" s="31"/>
+      <c r="G197" s="31"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:G25" etc:filterBottomFollowUsedRange="0">
@@ -2686,29 +2915,29 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="27.75" spans="1:8">
-      <c r="A2" s="11" t="s">
+    <row r="2" ht="13.9" spans="1:8">
+      <c r="A2" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2724,9 +2953,822 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="13.8849557522124" customWidth="1"/>
+    <col min="4" max="4" width="15.2654867256637" customWidth="1"/>
+    <col min="5" max="5" width="14.0796460176991" customWidth="1"/>
+    <col min="6" max="6" width="12.4159292035398" customWidth="1"/>
+    <col min="7" max="7" width="41.5575221238938" customWidth="1"/>
+    <col min="8" max="8" width="41.6902654867257" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="12.4" spans="3:8">
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="12.35" spans="1:8">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="11" customHeight="1" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" s="11" customFormat="1" ht="24.75" spans="1:21">
+      <c r="A4" s="12">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="14">
+        <v>3</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="24.75" spans="1:12">
+      <c r="A5" s="15">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16">
+        <v>2</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="17">
+        <v>3</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" ht="37.15" spans="1:8">
+      <c r="A6" s="18">
+        <v>3</v>
+      </c>
+      <c r="B6" s="19">
+        <v>3</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="19">
+        <v>3</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" ht="24.75" spans="1:8">
+      <c r="A7" s="15">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16">
+        <v>4</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="17">
+        <v>3</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" ht="24.75" spans="1:8">
+      <c r="A8" s="18">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19">
+        <v>5</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="20">
+        <v>3</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" ht="24.75" spans="1:8">
+      <c r="A9" s="15">
+        <v>6</v>
+      </c>
+      <c r="B9" s="16">
+        <v>6</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="16">
+        <v>3</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" ht="37.15" spans="1:8">
+      <c r="A10" s="18">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="20">
+        <v>3</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" ht="24.75" spans="1:8">
+      <c r="A11" s="15">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16">
+        <v>8</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="17">
+        <v>3</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" ht="37.15" spans="1:8">
+      <c r="A12" s="18">
+        <v>9</v>
+      </c>
+      <c r="B12" s="19">
+        <v>9</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="19">
+        <v>5</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" ht="37.15" spans="1:8">
+      <c r="A13" s="15">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16">
+        <v>10</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="17">
+        <v>3</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" ht="24.75" spans="1:8">
+      <c r="A14" s="18">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19">
+        <v>11</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="20">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="16">
+        <v>12</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="18">
+        <v>13</v>
+      </c>
+      <c r="B16" s="19">
+        <v>13</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="15">
+        <v>14</v>
+      </c>
+      <c r="B17" s="16">
+        <v>14</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="18">
+        <v>15</v>
+      </c>
+      <c r="B18" s="19">
+        <v>15</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="15">
+        <v>16</v>
+      </c>
+      <c r="B19" s="16">
+        <v>16</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="18">
+        <v>17</v>
+      </c>
+      <c r="B20" s="19">
+        <v>17</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="15">
+        <v>18</v>
+      </c>
+      <c r="B21" s="16">
+        <v>18</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="18">
+        <v>19</v>
+      </c>
+      <c r="B22" s="19">
+        <v>19</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="15">
+        <v>20</v>
+      </c>
+      <c r="B23" s="16">
+        <v>20</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="18">
+        <v>21</v>
+      </c>
+      <c r="B24" s="19">
+        <v>21</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="15">
+        <v>22</v>
+      </c>
+      <c r="B25" s="16">
+        <v>22</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="18">
+        <v>23</v>
+      </c>
+      <c r="B26" s="19">
+        <v>23</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="15">
+        <v>24</v>
+      </c>
+      <c r="B27" s="16">
+        <v>24</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+    </row>
+    <row r="28" ht="37.15" spans="1:8">
+      <c r="A28" s="18">
+        <v>25</v>
+      </c>
+      <c r="B28" s="19">
+        <v>25</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="20">
+        <v>3</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="15">
+        <v>26</v>
+      </c>
+      <c r="B29" s="16">
+        <v>26</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="18">
+        <v>27</v>
+      </c>
+      <c r="B30" s="19">
+        <v>27</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="15">
+        <v>28</v>
+      </c>
+      <c r="B31" s="16">
+        <v>28</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="18">
+        <v>29</v>
+      </c>
+      <c r="B32" s="19">
+        <v>29</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="15">
+        <v>30</v>
+      </c>
+      <c r="B33" s="16">
+        <v>30</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="11">
+        <v>31</v>
+      </c>
+      <c r="B34" s="11">
+        <v>31</v>
+      </c>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3">
+        <v>32</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="11">
+        <v>33</v>
+      </c>
+      <c r="B36" s="11">
+        <v>33</v>
+      </c>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3">
+        <v>34</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="11">
+        <v>35</v>
+      </c>
+      <c r="B38" s="11">
+        <v>35</v>
+      </c>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3">
+        <v>36</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="11">
+        <v>37</v>
+      </c>
+      <c r="B40" s="11">
+        <v>37</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3">
+        <v>38</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="11">
+        <v>39</v>
+      </c>
+      <c r="B42" s="11">
+        <v>39</v>
+      </c>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="3">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+    </row>
+    <row r="45" spans="5:5">
+      <c r="E45" s="16"/>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G45" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2777,102 +3819,102 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="12.4" spans="4:11">
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="12.4" spans="1:11">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="12.4" spans="1:12">
       <c r="A3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="49.5" spans="1:11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="24.75" spans="1:11">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -2880,10 +3922,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="E4" s="2">
         <v>60</v>
@@ -2901,13 +3943,13 @@
         <v>5</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="61.9" spans="1:11">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="37.15" spans="1:11">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -2915,10 +3957,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -2936,10 +3978,10 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="12.35" spans="11:11">
@@ -2954,7 +3996,6 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="1"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -2963,7 +4004,6 @@
       <c r="C9" s="3"/>
       <c r="D9" s="8"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="1"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -2972,7 +4012,6 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="1"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -2981,7 +4020,6 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="1"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -2990,7 +4028,6 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="1"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -2999,7 +4036,6 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="1"/>
       <c r="K13" s="10"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3008,7 +4044,6 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="1"/>
       <c r="K14" s="10"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3017,7 +4052,6 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="1"/>
       <c r="K15" s="10"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3026,7 +4060,6 @@
       <c r="C16" s="3"/>
       <c r="D16" s="8"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="1"/>
       <c r="K16" s="10"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3035,7 +4068,6 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="1"/>
       <c r="K17" s="10"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3044,7 +4076,6 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="1"/>
       <c r="K18" s="10"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3053,7 +4084,6 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="1"/>
       <c r="K19" s="10"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3062,7 +4092,6 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="1"/>
       <c r="K20" s="10"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="12.35" spans="1:11">
@@ -3071,7 +4100,6 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="1"/>
       <c r="K21" s="10"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="12.35" spans="1:5">

--- a/Doc/数据表总览.xlsx
+++ b/Doc/数据表总览.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18052" windowHeight="8655" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="关卡数据表" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="111">
   <si>
     <t>关卡序号</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>String</t>
-  </si>
-  <si>
-    <t>用来给程序看，不写入游戏展示给玩家</t>
   </si>
   <si>
     <t>Key</t>
@@ -1766,15 +1763,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G197"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="18.5221238938053" customWidth="1"/>
-    <col min="2" max="2" width="17.4601769911504" customWidth="1"/>
-    <col min="3" max="3" width="19.716814159292" customWidth="1"/>
-    <col min="4" max="4" width="21.8407079646018" customWidth="1"/>
-    <col min="5" max="5" width="28.2212389380531" customWidth="1"/>
-    <col min="6" max="6" width="26.0884955752212" customWidth="1"/>
-    <col min="7" max="7" width="13.283185840708" customWidth="1"/>
+    <col min="1" max="1" width="18.525" customWidth="1"/>
+    <col min="2" max="2" width="17.4583333333333" customWidth="1"/>
+    <col min="3" max="3" width="19.7166666666667" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" customWidth="1"/>
+    <col min="5" max="5" width="28.225" customWidth="1"/>
+    <col min="6" max="6" width="26.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="13.2833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="25" customFormat="1" spans="1:7">
@@ -1800,7 +1797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="26" customFormat="1" ht="13.9" spans="1:7">
+    <row r="2" s="26" customFormat="1" ht="14.25" spans="1:7">
       <c r="A2" s="28" t="s">
         <v>7</v>
       </c>
@@ -1823,7 +1820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="3" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A3" s="30">
         <v>1</v>
       </c>
@@ -1844,7 +1841,7 @@
       </c>
       <c r="G3" s="31"/>
     </row>
-    <row r="4" s="25" customFormat="1" ht="13.85" spans="1:6">
+    <row r="4" s="25" customFormat="1" ht="14.25" spans="1:6">
       <c r="A4" s="33">
         <v>1</v>
       </c>
@@ -1864,7 +1861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="5" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A5" s="30">
         <v>2</v>
       </c>
@@ -1885,7 +1882,7 @@
       </c>
       <c r="G5" s="31"/>
     </row>
-    <row r="6" s="25" customFormat="1" ht="13.85" spans="1:6">
+    <row r="6" s="25" customFormat="1" ht="14.25" spans="1:6">
       <c r="A6" s="33">
         <v>2</v>
       </c>
@@ -1905,7 +1902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="7" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A7" s="30"/>
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
@@ -1915,7 +1912,7 @@
       <c r="G7" s="31"/>
     </row>
     <row r="8" s="25" customFormat="1"/>
-    <row r="9" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="9" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A9" s="30"/>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
@@ -1925,7 +1922,7 @@
       <c r="G9" s="31"/>
     </row>
     <row r="10" s="25" customFormat="1"/>
-    <row r="11" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="11" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A11" s="30"/>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -1935,7 +1932,7 @@
       <c r="G11" s="31"/>
     </row>
     <row r="12" s="25" customFormat="1"/>
-    <row r="13" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="13" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A13" s="30"/>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
@@ -1945,7 +1942,7 @@
       <c r="G13" s="31"/>
     </row>
     <row r="14" s="25" customFormat="1"/>
-    <row r="15" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="15" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A15" s="30"/>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
@@ -1955,7 +1952,7 @@
       <c r="G15" s="31"/>
     </row>
     <row r="16" s="25" customFormat="1"/>
-    <row r="17" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="17" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A17" s="30"/>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
@@ -1965,7 +1962,7 @@
       <c r="G17" s="31"/>
     </row>
     <row r="18" s="25" customFormat="1"/>
-    <row r="19" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="19" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A19" s="30"/>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
@@ -1975,7 +1972,7 @@
       <c r="G19" s="31"/>
     </row>
     <row r="20" s="25" customFormat="1"/>
-    <row r="21" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="21" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A21" s="30"/>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1985,7 +1982,7 @@
       <c r="G21" s="31"/>
     </row>
     <row r="22" s="25" customFormat="1"/>
-    <row r="23" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="23" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A23" s="30"/>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
@@ -1995,7 +1992,7 @@
       <c r="G23" s="31"/>
     </row>
     <row r="24" s="25" customFormat="1"/>
-    <row r="25" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="25" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A25" s="30"/>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
@@ -2005,7 +2002,7 @@
       <c r="G25" s="31"/>
     </row>
     <row r="26" s="25" customFormat="1"/>
-    <row r="27" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="27" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A27" s="30"/>
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
@@ -2015,7 +2012,7 @@
       <c r="G27" s="31"/>
     </row>
     <row r="28" s="25" customFormat="1"/>
-    <row r="29" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="29" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A29" s="30"/>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -2025,7 +2022,7 @@
       <c r="G29" s="31"/>
     </row>
     <row r="30" s="25" customFormat="1"/>
-    <row r="31" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="31" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A31" s="30"/>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
@@ -2035,7 +2032,7 @@
       <c r="G31" s="31"/>
     </row>
     <row r="32" s="25" customFormat="1"/>
-    <row r="33" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="33" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A33" s="30"/>
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
@@ -2045,7 +2042,7 @@
       <c r="G33" s="31"/>
     </row>
     <row r="34" s="25" customFormat="1"/>
-    <row r="35" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="35" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A35" s="30"/>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
@@ -2055,7 +2052,7 @@
       <c r="G35" s="31"/>
     </row>
     <row r="36" s="25" customFormat="1"/>
-    <row r="37" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="37" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A37" s="30"/>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -2065,7 +2062,7 @@
       <c r="G37" s="31"/>
     </row>
     <row r="38" s="25" customFormat="1"/>
-    <row r="39" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="39" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A39" s="30"/>
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
@@ -2075,7 +2072,7 @@
       <c r="G39" s="31"/>
     </row>
     <row r="40" s="25" customFormat="1"/>
-    <row r="41" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="41" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A41" s="30"/>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
@@ -2085,7 +2082,7 @@
       <c r="G41" s="31"/>
     </row>
     <row r="42" s="25" customFormat="1"/>
-    <row r="43" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="43" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A43" s="30"/>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -2095,7 +2092,7 @@
       <c r="G43" s="31"/>
     </row>
     <row r="44" s="25" customFormat="1"/>
-    <row r="45" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="45" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A45" s="30"/>
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
@@ -2105,7 +2102,7 @@
       <c r="G45" s="31"/>
     </row>
     <row r="46" s="25" customFormat="1"/>
-    <row r="47" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="47" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A47" s="30"/>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
@@ -2115,7 +2112,7 @@
       <c r="G47" s="31"/>
     </row>
     <row r="48" s="25" customFormat="1"/>
-    <row r="49" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="49" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A49" s="30"/>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
@@ -2125,7 +2122,7 @@
       <c r="G49" s="31"/>
     </row>
     <row r="50" s="25" customFormat="1"/>
-    <row r="51" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="51" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A51" s="30"/>
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
@@ -2135,7 +2132,7 @@
       <c r="G51" s="31"/>
     </row>
     <row r="52" s="25" customFormat="1"/>
-    <row r="53" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="53" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A53" s="30"/>
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
@@ -2145,7 +2142,7 @@
       <c r="G53" s="31"/>
     </row>
     <row r="54" s="25" customFormat="1"/>
-    <row r="55" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="55" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A55" s="30"/>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
@@ -2155,7 +2152,7 @@
       <c r="G55" s="31"/>
     </row>
     <row r="56" s="25" customFormat="1"/>
-    <row r="57" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="57" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A57" s="30"/>
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
@@ -2165,7 +2162,7 @@
       <c r="G57" s="31"/>
     </row>
     <row r="58" s="25" customFormat="1"/>
-    <row r="59" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="59" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A59" s="30"/>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
@@ -2175,7 +2172,7 @@
       <c r="G59" s="31"/>
     </row>
     <row r="60" s="25" customFormat="1"/>
-    <row r="61" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="61" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A61" s="30"/>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -2185,7 +2182,7 @@
       <c r="G61" s="31"/>
     </row>
     <row r="62" s="25" customFormat="1"/>
-    <row r="63" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="63" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A63" s="30"/>
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
@@ -2195,7 +2192,7 @@
       <c r="G63" s="31"/>
     </row>
     <row r="64" s="25" customFormat="1"/>
-    <row r="65" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="65" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A65" s="30"/>
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
@@ -2205,7 +2202,7 @@
       <c r="G65" s="31"/>
     </row>
     <row r="66" s="25" customFormat="1"/>
-    <row r="67" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="67" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A67" s="30"/>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -2215,7 +2212,7 @@
       <c r="G67" s="31"/>
     </row>
     <row r="68" s="25" customFormat="1"/>
-    <row r="69" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="69" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A69" s="30"/>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
@@ -2225,7 +2222,7 @@
       <c r="G69" s="31"/>
     </row>
     <row r="70" s="25" customFormat="1"/>
-    <row r="71" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="71" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A71" s="30"/>
       <c r="B71" s="31"/>
       <c r="C71" s="31"/>
@@ -2235,7 +2232,7 @@
       <c r="G71" s="31"/>
     </row>
     <row r="72" s="25" customFormat="1"/>
-    <row r="73" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="73" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A73" s="30"/>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
@@ -2245,7 +2242,7 @@
       <c r="G73" s="31"/>
     </row>
     <row r="74" s="25" customFormat="1"/>
-    <row r="75" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="75" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A75" s="30"/>
       <c r="B75" s="31"/>
       <c r="C75" s="31"/>
@@ -2255,7 +2252,7 @@
       <c r="G75" s="31"/>
     </row>
     <row r="76" s="25" customFormat="1"/>
-    <row r="77" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="77" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A77" s="30"/>
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
@@ -2265,7 +2262,7 @@
       <c r="G77" s="31"/>
     </row>
     <row r="78" s="25" customFormat="1"/>
-    <row r="79" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="79" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A79" s="30"/>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
@@ -2275,7 +2272,7 @@
       <c r="G79" s="31"/>
     </row>
     <row r="80" s="25" customFormat="1"/>
-    <row r="81" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="81" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A81" s="30"/>
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
@@ -2285,7 +2282,7 @@
       <c r="G81" s="31"/>
     </row>
     <row r="82" s="25" customFormat="1"/>
-    <row r="83" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="83" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A83" s="30"/>
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
@@ -2295,7 +2292,7 @@
       <c r="G83" s="31"/>
     </row>
     <row r="84" s="25" customFormat="1"/>
-    <row r="85" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="85" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A85" s="30"/>
       <c r="B85" s="31"/>
       <c r="C85" s="31"/>
@@ -2305,7 +2302,7 @@
       <c r="G85" s="31"/>
     </row>
     <row r="86" s="25" customFormat="1"/>
-    <row r="87" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="87" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A87" s="30"/>
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
@@ -2315,7 +2312,7 @@
       <c r="G87" s="31"/>
     </row>
     <row r="88" s="25" customFormat="1"/>
-    <row r="89" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="89" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A89" s="30"/>
       <c r="B89" s="31"/>
       <c r="C89" s="31"/>
@@ -2325,7 +2322,7 @@
       <c r="G89" s="31"/>
     </row>
     <row r="90" s="25" customFormat="1"/>
-    <row r="91" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="91" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A91" s="30"/>
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
@@ -2335,7 +2332,7 @@
       <c r="G91" s="31"/>
     </row>
     <row r="92" s="25" customFormat="1"/>
-    <row r="93" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="93" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A93" s="30"/>
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
@@ -2345,7 +2342,7 @@
       <c r="G93" s="31"/>
     </row>
     <row r="94" s="25" customFormat="1"/>
-    <row r="95" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="95" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A95" s="30"/>
       <c r="B95" s="31"/>
       <c r="C95" s="31"/>
@@ -2355,7 +2352,7 @@
       <c r="G95" s="31"/>
     </row>
     <row r="96" s="25" customFormat="1"/>
-    <row r="97" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="97" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A97" s="30"/>
       <c r="B97" s="31"/>
       <c r="C97" s="31"/>
@@ -2365,7 +2362,7 @@
       <c r="G97" s="31"/>
     </row>
     <row r="98" s="25" customFormat="1"/>
-    <row r="99" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="99" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A99" s="30"/>
       <c r="B99" s="31"/>
       <c r="C99" s="31"/>
@@ -2375,7 +2372,7 @@
       <c r="G99" s="31"/>
     </row>
     <row r="100" s="25" customFormat="1"/>
-    <row r="101" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="101" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A101" s="30"/>
       <c r="B101" s="31"/>
       <c r="C101" s="31"/>
@@ -2385,7 +2382,7 @@
       <c r="G101" s="31"/>
     </row>
     <row r="102" s="25" customFormat="1"/>
-    <row r="103" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="103" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A103" s="30"/>
       <c r="B103" s="31"/>
       <c r="C103" s="31"/>
@@ -2395,7 +2392,7 @@
       <c r="G103" s="31"/>
     </row>
     <row r="104" s="25" customFormat="1"/>
-    <row r="105" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="105" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A105" s="30"/>
       <c r="B105" s="31"/>
       <c r="C105" s="31"/>
@@ -2405,7 +2402,7 @@
       <c r="G105" s="31"/>
     </row>
     <row r="106" s="25" customFormat="1"/>
-    <row r="107" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="107" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A107" s="30"/>
       <c r="B107" s="31"/>
       <c r="C107" s="31"/>
@@ -2415,7 +2412,7 @@
       <c r="G107" s="31"/>
     </row>
     <row r="108" s="25" customFormat="1"/>
-    <row r="109" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="109" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A109" s="30"/>
       <c r="B109" s="31"/>
       <c r="C109" s="31"/>
@@ -2425,7 +2422,7 @@
       <c r="G109" s="31"/>
     </row>
     <row r="110" s="25" customFormat="1"/>
-    <row r="111" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="111" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A111" s="30"/>
       <c r="B111" s="31"/>
       <c r="C111" s="31"/>
@@ -2435,7 +2432,7 @@
       <c r="G111" s="31"/>
     </row>
     <row r="112" s="25" customFormat="1"/>
-    <row r="113" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="113" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A113" s="30"/>
       <c r="B113" s="31"/>
       <c r="C113" s="31"/>
@@ -2445,7 +2442,7 @@
       <c r="G113" s="31"/>
     </row>
     <row r="114" s="25" customFormat="1"/>
-    <row r="115" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="115" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A115" s="30"/>
       <c r="B115" s="31"/>
       <c r="C115" s="31"/>
@@ -2455,7 +2452,7 @@
       <c r="G115" s="31"/>
     </row>
     <row r="116" s="25" customFormat="1"/>
-    <row r="117" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="117" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A117" s="30"/>
       <c r="B117" s="31"/>
       <c r="C117" s="31"/>
@@ -2465,7 +2462,7 @@
       <c r="G117" s="31"/>
     </row>
     <row r="118" s="25" customFormat="1"/>
-    <row r="119" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="119" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A119" s="30"/>
       <c r="B119" s="31"/>
       <c r="C119" s="31"/>
@@ -2475,7 +2472,7 @@
       <c r="G119" s="31"/>
     </row>
     <row r="120" s="25" customFormat="1"/>
-    <row r="121" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="121" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A121" s="30"/>
       <c r="B121" s="31"/>
       <c r="C121" s="31"/>
@@ -2485,7 +2482,7 @@
       <c r="G121" s="31"/>
     </row>
     <row r="122" s="25" customFormat="1"/>
-    <row r="123" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="123" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A123" s="30"/>
       <c r="B123" s="31"/>
       <c r="C123" s="31"/>
@@ -2495,7 +2492,7 @@
       <c r="G123" s="31"/>
     </row>
     <row r="124" s="25" customFormat="1"/>
-    <row r="125" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="125" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A125" s="30"/>
       <c r="B125" s="31"/>
       <c r="C125" s="31"/>
@@ -2505,7 +2502,7 @@
       <c r="G125" s="31"/>
     </row>
     <row r="126" s="25" customFormat="1"/>
-    <row r="127" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="127" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A127" s="30"/>
       <c r="B127" s="31"/>
       <c r="C127" s="31"/>
@@ -2515,7 +2512,7 @@
       <c r="G127" s="31"/>
     </row>
     <row r="128" s="25" customFormat="1"/>
-    <row r="129" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="129" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A129" s="30"/>
       <c r="B129" s="31"/>
       <c r="C129" s="31"/>
@@ -2525,7 +2522,7 @@
       <c r="G129" s="31"/>
     </row>
     <row r="130" s="25" customFormat="1"/>
-    <row r="131" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="131" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A131" s="30"/>
       <c r="B131" s="31"/>
       <c r="C131" s="31"/>
@@ -2535,7 +2532,7 @@
       <c r="G131" s="31"/>
     </row>
     <row r="132" s="25" customFormat="1"/>
-    <row r="133" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="133" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A133" s="30"/>
       <c r="B133" s="31"/>
       <c r="C133" s="31"/>
@@ -2545,7 +2542,7 @@
       <c r="G133" s="31"/>
     </row>
     <row r="134" s="25" customFormat="1"/>
-    <row r="135" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="135" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A135" s="30"/>
       <c r="B135" s="31"/>
       <c r="C135" s="31"/>
@@ -2555,7 +2552,7 @@
       <c r="G135" s="31"/>
     </row>
     <row r="136" s="25" customFormat="1"/>
-    <row r="137" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="137" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A137" s="30"/>
       <c r="B137" s="31"/>
       <c r="C137" s="31"/>
@@ -2565,7 +2562,7 @@
       <c r="G137" s="31"/>
     </row>
     <row r="138" s="25" customFormat="1"/>
-    <row r="139" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="139" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A139" s="30"/>
       <c r="B139" s="31"/>
       <c r="C139" s="31"/>
@@ -2575,7 +2572,7 @@
       <c r="G139" s="31"/>
     </row>
     <row r="140" s="25" customFormat="1"/>
-    <row r="141" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="141" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A141" s="30"/>
       <c r="B141" s="31"/>
       <c r="C141" s="31"/>
@@ -2585,7 +2582,7 @@
       <c r="G141" s="31"/>
     </row>
     <row r="142" s="25" customFormat="1"/>
-    <row r="143" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="143" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A143" s="30"/>
       <c r="B143" s="31"/>
       <c r="C143" s="31"/>
@@ -2595,7 +2592,7 @@
       <c r="G143" s="31"/>
     </row>
     <row r="144" s="25" customFormat="1"/>
-    <row r="145" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="145" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A145" s="30"/>
       <c r="B145" s="31"/>
       <c r="C145" s="31"/>
@@ -2605,7 +2602,7 @@
       <c r="G145" s="31"/>
     </row>
     <row r="146" s="25" customFormat="1"/>
-    <row r="147" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="147" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A147" s="30"/>
       <c r="B147" s="31"/>
       <c r="C147" s="31"/>
@@ -2615,7 +2612,7 @@
       <c r="G147" s="31"/>
     </row>
     <row r="148" s="25" customFormat="1"/>
-    <row r="149" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="149" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A149" s="30"/>
       <c r="B149" s="31"/>
       <c r="C149" s="31"/>
@@ -2625,7 +2622,7 @@
       <c r="G149" s="31"/>
     </row>
     <row r="150" s="25" customFormat="1"/>
-    <row r="151" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="151" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A151" s="30"/>
       <c r="B151" s="31"/>
       <c r="C151" s="31"/>
@@ -2635,7 +2632,7 @@
       <c r="G151" s="31"/>
     </row>
     <row r="152" s="25" customFormat="1"/>
-    <row r="153" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="153" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A153" s="30"/>
       <c r="B153" s="31"/>
       <c r="C153" s="31"/>
@@ -2645,7 +2642,7 @@
       <c r="G153" s="31"/>
     </row>
     <row r="154" s="25" customFormat="1"/>
-    <row r="155" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="155" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A155" s="30"/>
       <c r="B155" s="31"/>
       <c r="C155" s="31"/>
@@ -2655,7 +2652,7 @@
       <c r="G155" s="31"/>
     </row>
     <row r="156" s="25" customFormat="1"/>
-    <row r="157" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="157" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A157" s="30"/>
       <c r="B157" s="31"/>
       <c r="C157" s="31"/>
@@ -2665,7 +2662,7 @@
       <c r="G157" s="31"/>
     </row>
     <row r="158" s="25" customFormat="1"/>
-    <row r="159" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="159" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A159" s="30"/>
       <c r="B159" s="31"/>
       <c r="C159" s="31"/>
@@ -2675,7 +2672,7 @@
       <c r="G159" s="31"/>
     </row>
     <row r="160" s="25" customFormat="1"/>
-    <row r="161" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="161" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A161" s="30"/>
       <c r="B161" s="31"/>
       <c r="C161" s="31"/>
@@ -2685,7 +2682,7 @@
       <c r="G161" s="31"/>
     </row>
     <row r="162" s="25" customFormat="1"/>
-    <row r="163" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="163" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A163" s="30"/>
       <c r="B163" s="31"/>
       <c r="C163" s="31"/>
@@ -2695,7 +2692,7 @@
       <c r="G163" s="31"/>
     </row>
     <row r="164" s="25" customFormat="1"/>
-    <row r="165" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="165" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A165" s="30"/>
       <c r="B165" s="31"/>
       <c r="C165" s="31"/>
@@ -2705,7 +2702,7 @@
       <c r="G165" s="31"/>
     </row>
     <row r="166" s="25" customFormat="1"/>
-    <row r="167" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="167" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A167" s="30"/>
       <c r="B167" s="31"/>
       <c r="C167" s="31"/>
@@ -2715,7 +2712,7 @@
       <c r="G167" s="31"/>
     </row>
     <row r="168" s="25" customFormat="1"/>
-    <row r="169" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="169" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A169" s="30"/>
       <c r="B169" s="31"/>
       <c r="C169" s="31"/>
@@ -2725,7 +2722,7 @@
       <c r="G169" s="31"/>
     </row>
     <row r="170" s="25" customFormat="1"/>
-    <row r="171" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="171" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A171" s="30"/>
       <c r="B171" s="31"/>
       <c r="C171" s="31"/>
@@ -2735,7 +2732,7 @@
       <c r="G171" s="31"/>
     </row>
     <row r="172" s="25" customFormat="1"/>
-    <row r="173" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="173" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A173" s="30"/>
       <c r="B173" s="31"/>
       <c r="C173" s="31"/>
@@ -2745,7 +2742,7 @@
       <c r="G173" s="31"/>
     </row>
     <row r="174" s="25" customFormat="1"/>
-    <row r="175" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="175" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A175" s="30"/>
       <c r="B175" s="31"/>
       <c r="C175" s="31"/>
@@ -2755,7 +2752,7 @@
       <c r="G175" s="31"/>
     </row>
     <row r="176" s="25" customFormat="1"/>
-    <row r="177" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="177" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A177" s="30"/>
       <c r="B177" s="31"/>
       <c r="C177" s="31"/>
@@ -2765,7 +2762,7 @@
       <c r="G177" s="31"/>
     </row>
     <row r="178" s="25" customFormat="1"/>
-    <row r="179" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="179" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A179" s="30"/>
       <c r="B179" s="31"/>
       <c r="C179" s="31"/>
@@ -2775,7 +2772,7 @@
       <c r="G179" s="31"/>
     </row>
     <row r="180" s="25" customFormat="1"/>
-    <row r="181" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="181" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A181" s="30"/>
       <c r="B181" s="31"/>
       <c r="C181" s="31"/>
@@ -2785,7 +2782,7 @@
       <c r="G181" s="31"/>
     </row>
     <row r="182" s="25" customFormat="1"/>
-    <row r="183" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="183" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A183" s="30"/>
       <c r="B183" s="31"/>
       <c r="C183" s="31"/>
@@ -2795,7 +2792,7 @@
       <c r="G183" s="31"/>
     </row>
     <row r="184" s="25" customFormat="1"/>
-    <row r="185" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="185" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A185" s="30"/>
       <c r="B185" s="31"/>
       <c r="C185" s="31"/>
@@ -2805,7 +2802,7 @@
       <c r="G185" s="31"/>
     </row>
     <row r="186" s="25" customFormat="1"/>
-    <row r="187" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="187" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A187" s="30"/>
       <c r="B187" s="31"/>
       <c r="C187" s="31"/>
@@ -2815,7 +2812,7 @@
       <c r="G187" s="31"/>
     </row>
     <row r="188" s="25" customFormat="1"/>
-    <row r="189" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="189" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A189" s="30"/>
       <c r="B189" s="31"/>
       <c r="C189" s="31"/>
@@ -2825,7 +2822,7 @@
       <c r="G189" s="31"/>
     </row>
     <row r="190" s="25" customFormat="1"/>
-    <row r="191" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="191" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A191" s="30"/>
       <c r="B191" s="31"/>
       <c r="C191" s="31"/>
@@ -2835,7 +2832,7 @@
       <c r="G191" s="31"/>
     </row>
     <row r="192" s="25" customFormat="1"/>
-    <row r="193" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="193" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A193" s="30"/>
       <c r="B193" s="31"/>
       <c r="C193" s="31"/>
@@ -2845,7 +2842,7 @@
       <c r="G193" s="31"/>
     </row>
     <row r="194" s="25" customFormat="1"/>
-    <row r="195" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="195" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A195" s="30"/>
       <c r="B195" s="31"/>
       <c r="C195" s="31"/>
@@ -2855,7 +2852,7 @@
       <c r="G195" s="31"/>
     </row>
     <row r="196" s="25" customFormat="1"/>
-    <row r="197" s="25" customFormat="1" ht="13.85" spans="1:7">
+    <row r="197" s="25" customFormat="1" ht="14.25" spans="1:7">
       <c r="A197" s="30"/>
       <c r="B197" s="31"/>
       <c r="C197" s="31"/>
@@ -2877,16 +2874,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="23.1769911504425" customWidth="1"/>
-    <col min="2" max="2" width="29.4070796460177" customWidth="1"/>
-    <col min="3" max="3" width="19.9203539823009" customWidth="1"/>
-    <col min="4" max="4" width="22.5752212389381" customWidth="1"/>
-    <col min="5" max="5" width="15.212389380531" customWidth="1"/>
-    <col min="6" max="6" width="23.3716814159292" customWidth="1"/>
-    <col min="7" max="7" width="16.1327433628319" customWidth="1"/>
-    <col min="8" max="8" width="18.9911504424779" customWidth="1"/>
+    <col min="1" max="1" width="23.175" customWidth="1"/>
+    <col min="2" max="2" width="29.4083333333333" customWidth="1"/>
+    <col min="3" max="3" width="19.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.575" customWidth="1"/>
+    <col min="5" max="5" width="15.2083333333333" customWidth="1"/>
+    <col min="6" max="6" width="23.375" customWidth="1"/>
+    <col min="7" max="7" width="16.1333333333333" customWidth="1"/>
+    <col min="8" max="8" width="18.9916666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2915,7 +2912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="13.9" spans="1:8">
+    <row r="2" ht="14.25" spans="1:8">
       <c r="A2" s="24" t="s">
         <v>22</v>
       </c>
@@ -2954,17 +2951,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U45"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="13.8849557522124" customWidth="1"/>
-    <col min="4" max="4" width="15.2654867256637" customWidth="1"/>
-    <col min="5" max="5" width="14.0796460176991" customWidth="1"/>
-    <col min="6" max="6" width="12.4159292035398" customWidth="1"/>
-    <col min="7" max="7" width="41.5575221238938" customWidth="1"/>
-    <col min="8" max="8" width="41.6902654867257" customWidth="1"/>
+    <col min="3" max="3" width="13.8833333333333" customWidth="1"/>
+    <col min="4" max="4" width="15.2666666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="41.5583333333333" customWidth="1"/>
+    <col min="8" max="8" width="41.6916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12.4" spans="3:8">
+    <row r="1" s="1" customFormat="1" ht="28.5" spans="3:8">
       <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2984,7 +2981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="12.35" spans="1:8">
+    <row r="2" s="1" customFormat="1" ht="14.25" spans="1:8">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>36</v>
@@ -3005,34 +3002,34 @@
         <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="11" customHeight="1" spans="1:8">
       <c r="A3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" s="11" customFormat="1" ht="24.75" spans="1:21">
+    <row r="4" s="11" customFormat="1" ht="28.5" spans="1:21">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -3040,22 +3037,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="F4" s="14">
         <v>3</v>
       </c>
       <c r="G4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3071,7 +3068,7 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
     </row>
-    <row r="5" s="3" customFormat="1" ht="24.75" spans="1:12">
+    <row r="5" s="3" customFormat="1" ht="28.5" spans="1:12">
       <c r="A5" s="15">
         <v>2</v>
       </c>
@@ -3079,28 +3076,28 @@
         <v>2</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>52</v>
-      </c>
       <c r="E5" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="17">
         <v>3</v>
       </c>
       <c r="G5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>54</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="L5" s="23"/>
     </row>
-    <row r="6" ht="37.15" spans="1:8">
+    <row r="6" ht="42.75" spans="1:8">
       <c r="A6" s="18">
         <v>3</v>
       </c>
@@ -3108,25 +3105,25 @@
         <v>3</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="F6" s="19">
         <v>3</v>
       </c>
       <c r="G6" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" ht="24.75" spans="1:8">
+    </row>
+    <row r="7" ht="28.5" spans="1:8">
       <c r="A7" s="15">
         <v>4</v>
       </c>
@@ -3134,25 +3131,25 @@
         <v>4</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" s="17">
         <v>3</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" ht="24.75" spans="1:8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:8">
       <c r="A8" s="18">
         <v>5</v>
       </c>
@@ -3160,25 +3157,25 @@
         <v>5</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="20">
         <v>3</v>
       </c>
       <c r="G8" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="24.75" spans="1:8">
+    </row>
+    <row r="9" ht="28.5" spans="1:8">
       <c r="A9" s="15">
         <v>6</v>
       </c>
@@ -3186,25 +3183,25 @@
         <v>6</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="16">
         <v>3</v>
       </c>
       <c r="G9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" ht="37.15" spans="1:8">
+    </row>
+    <row r="10" ht="42.75" spans="1:8">
       <c r="A10" s="18">
         <v>7</v>
       </c>
@@ -3212,25 +3209,25 @@
         <v>7</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="20">
         <v>3</v>
       </c>
       <c r="G10" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" ht="24.75" spans="1:8">
+    </row>
+    <row r="11" ht="42.75" spans="1:8">
       <c r="A11" s="15">
         <v>8</v>
       </c>
@@ -3238,25 +3235,25 @@
         <v>8</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="17">
         <v>3</v>
       </c>
       <c r="G11" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" ht="37.15" spans="1:8">
+    </row>
+    <row r="12" ht="42.75" spans="1:8">
       <c r="A12" s="18">
         <v>9</v>
       </c>
@@ -3264,25 +3261,25 @@
         <v>9</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="19">
         <v>5</v>
       </c>
       <c r="G12" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" ht="37.15" spans="1:8">
+    </row>
+    <row r="13" ht="42.75" spans="1:8">
       <c r="A13" s="15">
         <v>10</v>
       </c>
@@ -3290,25 +3287,25 @@
         <v>10</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="17">
         <v>3</v>
       </c>
       <c r="G13" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" ht="24.75" spans="1:8">
+    </row>
+    <row r="14" ht="28.5" spans="1:8">
       <c r="A14" s="18">
         <v>11</v>
       </c>
@@ -3316,25 +3313,25 @@
         <v>11</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="20">
         <v>1</v>
       </c>
       <c r="G14" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H14" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+    </row>
+    <row r="15" ht="14.25" spans="1:8">
       <c r="A15" s="15">
         <v>12</v>
       </c>
@@ -3348,7 +3345,7 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" ht="14.25" spans="1:8">
       <c r="A16" s="18">
         <v>13</v>
       </c>
@@ -3362,7 +3359,7 @@
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" ht="14.25" spans="1:8">
       <c r="A17" s="15">
         <v>14</v>
       </c>
@@ -3376,7 +3373,7 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" ht="14.25" spans="1:8">
       <c r="A18" s="18">
         <v>15</v>
       </c>
@@ -3390,7 +3387,7 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" ht="14.25" spans="1:8">
       <c r="A19" s="15">
         <v>16</v>
       </c>
@@ -3404,7 +3401,7 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" ht="14.25" spans="1:8">
       <c r="A20" s="18">
         <v>17</v>
       </c>
@@ -3418,7 +3415,7 @@
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" ht="14.25" spans="1:8">
       <c r="A21" s="15">
         <v>18</v>
       </c>
@@ -3432,7 +3429,7 @@
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" ht="14.25" spans="1:8">
       <c r="A22" s="18">
         <v>19</v>
       </c>
@@ -3446,7 +3443,7 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" ht="14.25" spans="1:8">
       <c r="A23" s="15">
         <v>20</v>
       </c>
@@ -3460,7 +3457,7 @@
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" ht="14.25" spans="1:8">
       <c r="A24" s="18">
         <v>21</v>
       </c>
@@ -3474,7 +3471,7 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="14.25" spans="1:8">
       <c r="A25" s="15">
         <v>22</v>
       </c>
@@ -3488,7 +3485,7 @@
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" ht="14.25" spans="1:8">
       <c r="A26" s="18">
         <v>23</v>
       </c>
@@ -3502,7 +3499,7 @@
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" ht="14.25" spans="1:8">
       <c r="A27" s="15">
         <v>24</v>
       </c>
@@ -3516,7 +3513,7 @@
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
     </row>
-    <row r="28" ht="37.15" spans="1:8">
+    <row r="28" ht="42.75" spans="1:8">
       <c r="A28" s="18">
         <v>25</v>
       </c>
@@ -3524,25 +3521,25 @@
         <v>25</v>
       </c>
       <c r="C28" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="F28" s="20">
         <v>3</v>
       </c>
       <c r="G28" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+    </row>
+    <row r="29" ht="14.25" spans="1:8">
       <c r="A29" s="15">
         <v>26</v>
       </c>
@@ -3556,7 +3553,7 @@
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" ht="14.25" spans="1:8">
       <c r="A30" s="18">
         <v>27</v>
       </c>
@@ -3570,7 +3567,7 @@
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" ht="14.25" spans="1:8">
       <c r="A31" s="15">
         <v>28</v>
       </c>
@@ -3584,7 +3581,7 @@
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" ht="14.25" spans="1:8">
       <c r="A32" s="18">
         <v>29</v>
       </c>
@@ -3598,7 +3595,7 @@
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" ht="14.25" spans="1:8">
       <c r="A33" s="15">
         <v>30</v>
       </c>
@@ -3612,7 +3609,7 @@
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" ht="14.25" spans="1:8">
       <c r="A34" s="11">
         <v>31</v>
       </c>
@@ -3626,7 +3623,7 @@
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" ht="14.25" spans="1:8">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -3640,7 +3637,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" ht="14.25" spans="1:8">
       <c r="A36" s="11">
         <v>33</v>
       </c>
@@ -3654,7 +3651,7 @@
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" ht="14.25" spans="1:8">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -3668,7 +3665,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" ht="14.25" spans="1:8">
       <c r="A38" s="11">
         <v>35</v>
       </c>
@@ -3682,7 +3679,7 @@
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" ht="14.25" spans="1:8">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -3696,7 +3693,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" ht="14.25" spans="1:8">
       <c r="A40" s="11">
         <v>37</v>
       </c>
@@ -3710,7 +3707,7 @@
       <c r="G40" s="22"/>
       <c r="H40" s="22"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" ht="14.25" spans="1:8">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -3724,7 +3721,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" ht="14.25" spans="1:8">
       <c r="A42" s="11">
         <v>39</v>
       </c>
@@ -3738,7 +3735,7 @@
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" ht="14.25" spans="1:8">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -3752,7 +3749,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" ht="14.25" spans="1:8">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -3762,7 +3759,7 @@
       <c r="G44" s="22"/>
       <c r="H44" s="22"/>
     </row>
-    <row r="45" spans="5:5">
+    <row r="45" ht="14.25" spans="5:5">
       <c r="E45" s="16"/>
     </row>
   </sheetData>
@@ -3778,7 +3775,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3789,7 +3786,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3800,7 +3797,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3811,39 +3808,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <cols>
-    <col min="10" max="10" width="21.5132743362832" customWidth="1"/>
-    <col min="11" max="11" width="34.2566371681416" customWidth="1"/>
+    <col min="10" max="10" width="21.5166666666667" customWidth="1"/>
+    <col min="11" max="11" width="34.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12.4" spans="4:11">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="4:11">
       <c r="D1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="12.4" spans="1:11">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>36</v>
@@ -3855,19 +3852,19 @@
         <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>37</v>
@@ -3876,45 +3873,45 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="12.4" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="D3" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="24.75" spans="1:11">
+    </row>
+    <row r="4" s="2" customFormat="1" ht="28.5" spans="1:11">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -3922,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="E4" s="2">
         <v>60</v>
@@ -3943,13 +3940,13 @@
         <v>5</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="37.15" spans="1:11">
+    </row>
+    <row r="5" s="2" customFormat="1" ht="42.75" spans="1:11">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -3957,10 +3954,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -3978,19 +3975,19 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="12.35" spans="11:11">
+    </row>
+    <row r="6" s="3" customFormat="1" ht="14.25" spans="11:11">
       <c r="K6" s="10"/>
     </row>
-    <row r="7" s="3" customFormat="1" ht="12.35" spans="11:11">
+    <row r="7" s="3" customFormat="1" ht="14.25" spans="11:11">
       <c r="K7" s="10"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="8" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3998,7 +3995,7 @@
       <c r="E8" s="4"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="9" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4006,7 +4003,7 @@
       <c r="E9" s="4"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="10" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4014,7 +4011,7 @@
       <c r="E10" s="4"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="11" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4022,7 +4019,7 @@
       <c r="E11" s="4"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="12" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4030,7 +4027,7 @@
       <c r="E12" s="4"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="13" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -4038,7 +4035,7 @@
       <c r="E13" s="4"/>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="14" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
@@ -4046,7 +4043,7 @@
       <c r="E14" s="4"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="15" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -4054,7 +4051,7 @@
       <c r="E15" s="4"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="16" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
@@ -4062,7 +4059,7 @@
       <c r="E16" s="4"/>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="17" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
@@ -4070,7 +4067,7 @@
       <c r="E17" s="4"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="18" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
@@ -4078,7 +4075,7 @@
       <c r="E18" s="4"/>
       <c r="K18" s="10"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="19" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -4086,7 +4083,7 @@
       <c r="E19" s="4"/>
       <c r="K19" s="10"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="20" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -4094,7 +4091,7 @@
       <c r="E20" s="4"/>
       <c r="K20" s="10"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="12.35" spans="1:11">
+    <row r="21" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -4102,161 +4099,161 @@
       <c r="E21" s="4"/>
       <c r="K21" s="10"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="22" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="23" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="8"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="24" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="25" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="26" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="27" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="28" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="29" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="30" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
       <c r="D30" s="8"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="31" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="32" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="33" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="4"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="34" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="35" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="36" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="37" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
       <c r="D37" s="8"/>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="38" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="39" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="4"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="40" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="41" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="4"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="42" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="43" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="12.35" spans="1:5">
+    <row r="44" s="1" customFormat="1" ht="14.25" spans="1:5">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>

--- a/Doc/数据表总览.xlsx
+++ b/Doc/数据表总览.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18052" windowHeight="8655" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="18052" windowHeight="8655" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="关卡数据表" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,8 @@
     <sheet name="卡牌数据表" sheetId="3" r:id="rId3"/>
     <sheet name="宝物数据表" sheetId="4" r:id="rId4"/>
     <sheet name="道具数据表" sheetId="5" r:id="rId5"/>
-    <sheet name="宠物数据表" sheetId="6" r:id="rId6"/>
-    <sheet name="武器数据表" sheetId="7" r:id="rId7"/>
+    <sheet name="武器数据表" sheetId="7" r:id="rId6"/>
+    <sheet name="天赋数据表" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">关卡数据表!$A$2:$G$25</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="227">
   <si>
     <t>关卡序号</t>
   </si>
@@ -530,6 +530,195 @@
   </si>
   <si>
     <t>向攻击范围内距离最近的敌人发射弹幕，对目标造成80%的AP伤害，对攻击范围内的所有敌人造成20%的AP伤害</t>
+  </si>
+  <si>
+    <t>名称（可以没有）</t>
+  </si>
+  <si>
+    <t>天赋种类</t>
+  </si>
+  <si>
+    <t>天赋等级</t>
+  </si>
+  <si>
+    <t>影响属性</t>
+  </si>
+  <si>
+    <t>天赋数值</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>基础天赋1</t>
+  </si>
+  <si>
+    <t>基础天赋2</t>
+  </si>
+  <si>
+    <t>基础天赋3</t>
+  </si>
+  <si>
+    <t>基础天赋4</t>
+  </si>
+  <si>
+    <t>基础天赋5</t>
+  </si>
+  <si>
+    <t>基础天赋6</t>
+  </si>
+  <si>
+    <t>基础天赋7</t>
+  </si>
+  <si>
+    <t>乾天赋1</t>
+  </si>
+  <si>
+    <t>乾天赋2</t>
+  </si>
+  <si>
+    <t>乾天赋3</t>
+  </si>
+  <si>
+    <t>乾天赋4</t>
+  </si>
+  <si>
+    <t>乾天赋5</t>
+  </si>
+  <si>
+    <t>乾天赋6</t>
+  </si>
+  <si>
+    <t>坎天赋1</t>
+  </si>
+  <si>
+    <t>坎天赋2</t>
+  </si>
+  <si>
+    <t>坎天赋3</t>
+  </si>
+  <si>
+    <t>坎天赋4</t>
+  </si>
+  <si>
+    <t>坎天赋5</t>
+  </si>
+  <si>
+    <t>坎天赋6</t>
+  </si>
+  <si>
+    <t>艮天赋1</t>
+  </si>
+  <si>
+    <t>艮天赋2</t>
+  </si>
+  <si>
+    <t>艮天赋3</t>
+  </si>
+  <si>
+    <t>艮天赋4</t>
+  </si>
+  <si>
+    <t>艮天赋5</t>
+  </si>
+  <si>
+    <t>艮天赋6</t>
+  </si>
+  <si>
+    <t>震天赋1</t>
+  </si>
+  <si>
+    <t>震天赋2</t>
+  </si>
+  <si>
+    <t>震天赋3</t>
+  </si>
+  <si>
+    <t>震天赋4</t>
+  </si>
+  <si>
+    <t>震天赋5</t>
+  </si>
+  <si>
+    <t>震天赋6</t>
+  </si>
+  <si>
+    <t>巽天赋1</t>
+  </si>
+  <si>
+    <t>巽天赋2</t>
+  </si>
+  <si>
+    <t>巽天赋3</t>
+  </si>
+  <si>
+    <t>巽天赋4</t>
+  </si>
+  <si>
+    <t>巽天赋5</t>
+  </si>
+  <si>
+    <t>巽天赋6</t>
+  </si>
+  <si>
+    <t>离天赋1</t>
+  </si>
+  <si>
+    <t>离天赋2</t>
+  </si>
+  <si>
+    <t>离天赋3</t>
+  </si>
+  <si>
+    <t>离天赋4</t>
+  </si>
+  <si>
+    <t>离天赋5</t>
+  </si>
+  <si>
+    <t>离天赋6</t>
+  </si>
+  <si>
+    <t>坤天赋1</t>
+  </si>
+  <si>
+    <t>坤天赋2</t>
+  </si>
+  <si>
+    <t>坤天赋3</t>
+  </si>
+  <si>
+    <t>坤天赋4</t>
+  </si>
+  <si>
+    <t>坤天赋5</t>
+  </si>
+  <si>
+    <t>坤天赋6</t>
+  </si>
+  <si>
+    <t>兑天赋1</t>
+  </si>
+  <si>
+    <t>兑天赋2</t>
+  </si>
+  <si>
+    <t>兑天赋3</t>
+  </si>
+  <si>
+    <t>兑天赋4</t>
+  </si>
+  <si>
+    <t>兑天赋5</t>
+  </si>
+  <si>
+    <t>兑天赋6</t>
   </si>
 </sst>
 </file>
@@ -542,7 +731,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,6 +741,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -566,20 +762,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -772,6 +954,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -845,12 +1033,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -987,12 +1169,49 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1191,207 +1410,228 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1403,28 +1643,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1433,28 +1673,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1994,1092 +2234,1092 @@
     <col min="7" max="7" width="13.3362831858407" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="36" customFormat="1" spans="1:7">
-      <c r="A1" s="38" t="s">
+    <row r="1" s="43" customFormat="1" spans="1:7">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="45" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="37" customFormat="1" ht="13.9" spans="1:7">
-      <c r="A2" s="39" t="s">
+    <row r="2" s="44" customFormat="1" ht="13.9" spans="1:7">
+      <c r="A2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="46" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A3" s="41">
+    <row r="3" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A3" s="48">
         <v>1</v>
       </c>
-      <c r="B3" s="42">
+      <c r="B3" s="49">
         <v>40</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="50">
         <v>0</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="49">
         <v>3</v>
       </c>
-      <c r="E3" s="42">
+      <c r="E3" s="49">
         <v>1</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="49">
         <v>5</v>
       </c>
-      <c r="G3" s="42"/>
-    </row>
-    <row r="4" s="36" customFormat="1" ht="13.85" spans="1:6">
-      <c r="A4" s="44">
+      <c r="G3" s="49"/>
+    </row>
+    <row r="4" s="43" customFormat="1" ht="13.85" spans="1:6">
+      <c r="A4" s="51">
         <v>1</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="43">
         <v>40</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="43">
         <v>20</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="43">
         <v>2</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="43">
         <v>1</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="43">
         <v>4</v>
       </c>
     </row>
-    <row r="5" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A5" s="41">
+    <row r="5" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A5" s="48">
         <v>2</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="49">
         <v>40</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="49">
         <v>0</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="49">
         <v>3</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="49">
         <v>1</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="49">
         <v>5</v>
       </c>
-      <c r="G5" s="42"/>
-    </row>
-    <row r="6" s="36" customFormat="1" ht="13.85" spans="1:6">
-      <c r="A6" s="44">
+      <c r="G5" s="49"/>
+    </row>
+    <row r="6" s="43" customFormat="1" ht="13.85" spans="1:6">
+      <c r="A6" s="51">
         <v>2</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="43">
         <v>40</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="43">
         <v>10</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="43">
         <v>2</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="43">
         <v>1</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="43">
         <v>5</v>
       </c>
     </row>
-    <row r="7" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A7" s="41"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-    </row>
-    <row r="8" s="36" customFormat="1"/>
-    <row r="9" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A9" s="41"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-    </row>
-    <row r="10" s="36" customFormat="1"/>
-    <row r="11" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A11" s="41"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-    </row>
-    <row r="12" s="36" customFormat="1"/>
-    <row r="13" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A13" s="41"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-    </row>
-    <row r="14" s="36" customFormat="1"/>
-    <row r="15" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A15" s="41"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-    </row>
-    <row r="16" s="36" customFormat="1"/>
-    <row r="17" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A17" s="41"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-    </row>
-    <row r="18" s="36" customFormat="1"/>
-    <row r="19" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A19" s="41"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20" s="36" customFormat="1"/>
-    <row r="21" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A21" s="41"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-    </row>
-    <row r="22" s="36" customFormat="1"/>
-    <row r="23" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A23" s="41"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-    </row>
-    <row r="24" s="36" customFormat="1"/>
-    <row r="25" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-    </row>
-    <row r="26" s="36" customFormat="1"/>
-    <row r="27" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-    </row>
-    <row r="28" s="36" customFormat="1"/>
-    <row r="29" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-    </row>
-    <row r="30" s="36" customFormat="1"/>
-    <row r="31" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A31" s="41"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-    </row>
-    <row r="32" s="36" customFormat="1"/>
-    <row r="33" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A33" s="41"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-    </row>
-    <row r="34" s="36" customFormat="1"/>
-    <row r="35" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-    </row>
-    <row r="36" s="36" customFormat="1"/>
-    <row r="37" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-    </row>
-    <row r="38" s="36" customFormat="1"/>
-    <row r="39" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A39" s="41"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-    </row>
-    <row r="40" s="36" customFormat="1"/>
-    <row r="41" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A41" s="41"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-    </row>
-    <row r="42" s="36" customFormat="1"/>
-    <row r="43" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A43" s="41"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-    </row>
-    <row r="44" s="36" customFormat="1"/>
-    <row r="45" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
-    </row>
-    <row r="46" s="36" customFormat="1"/>
-    <row r="47" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A47" s="41"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-    </row>
-    <row r="48" s="36" customFormat="1"/>
-    <row r="49" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="42"/>
-    </row>
-    <row r="50" s="36" customFormat="1"/>
-    <row r="51" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A51" s="41"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-    </row>
-    <row r="52" s="36" customFormat="1"/>
-    <row r="53" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A53" s="41"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-    </row>
-    <row r="54" s="36" customFormat="1"/>
-    <row r="55" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A55" s="41"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-    </row>
-    <row r="56" s="36" customFormat="1"/>
-    <row r="57" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A57" s="41"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-    </row>
-    <row r="58" s="36" customFormat="1"/>
-    <row r="59" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A59" s="41"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-    </row>
-    <row r="60" s="36" customFormat="1"/>
-    <row r="61" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A61" s="41"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="42"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-    </row>
-    <row r="62" s="36" customFormat="1"/>
-    <row r="63" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A63" s="41"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-    </row>
-    <row r="64" s="36" customFormat="1"/>
-    <row r="65" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A65" s="41"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-    </row>
-    <row r="66" s="36" customFormat="1"/>
-    <row r="67" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A67" s="41"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-    </row>
-    <row r="68" s="36" customFormat="1"/>
-    <row r="69" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A69" s="41"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-    </row>
-    <row r="70" s="36" customFormat="1"/>
-    <row r="71" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A71" s="41"/>
-      <c r="B71" s="42"/>
-      <c r="C71" s="42"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-      <c r="G71" s="42"/>
-    </row>
-    <row r="72" s="36" customFormat="1"/>
-    <row r="73" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A73" s="41"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="42"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="42"/>
-    </row>
-    <row r="74" s="36" customFormat="1"/>
-    <row r="75" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A75" s="41"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="42"/>
-    </row>
-    <row r="76" s="36" customFormat="1"/>
-    <row r="77" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A77" s="41"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="42"/>
-    </row>
-    <row r="78" s="36" customFormat="1"/>
-    <row r="79" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A79" s="41"/>
-      <c r="B79" s="42"/>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="42"/>
-    </row>
-    <row r="80" s="36" customFormat="1"/>
-    <row r="81" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A81" s="41"/>
-      <c r="B81" s="42"/>
-      <c r="C81" s="42"/>
-      <c r="D81" s="42"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="42"/>
-      <c r="G81" s="42"/>
-    </row>
-    <row r="82" s="36" customFormat="1"/>
-    <row r="83" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A83" s="41"/>
-      <c r="B83" s="42"/>
-      <c r="C83" s="42"/>
-      <c r="D83" s="42"/>
-      <c r="E83" s="42"/>
-      <c r="F83" s="42"/>
-      <c r="G83" s="42"/>
-    </row>
-    <row r="84" s="36" customFormat="1"/>
-    <row r="85" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A85" s="41"/>
-      <c r="B85" s="42"/>
-      <c r="C85" s="42"/>
-      <c r="D85" s="42"/>
-      <c r="E85" s="42"/>
-      <c r="F85" s="42"/>
-      <c r="G85" s="42"/>
-    </row>
-    <row r="86" s="36" customFormat="1"/>
-    <row r="87" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A87" s="41"/>
-      <c r="B87" s="42"/>
-      <c r="C87" s="42"/>
-      <c r="D87" s="42"/>
-      <c r="E87" s="42"/>
-      <c r="F87" s="42"/>
-      <c r="G87" s="42"/>
-    </row>
-    <row r="88" s="36" customFormat="1"/>
-    <row r="89" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A89" s="41"/>
-      <c r="B89" s="42"/>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="42"/>
-    </row>
-    <row r="90" s="36" customFormat="1"/>
-    <row r="91" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A91" s="41"/>
-      <c r="B91" s="42"/>
-      <c r="C91" s="42"/>
-      <c r="D91" s="42"/>
-      <c r="E91" s="42"/>
-      <c r="F91" s="42"/>
-      <c r="G91" s="42"/>
-    </row>
-    <row r="92" s="36" customFormat="1"/>
-    <row r="93" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A93" s="41"/>
-      <c r="B93" s="42"/>
-      <c r="C93" s="42"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="42"/>
-      <c r="F93" s="42"/>
-      <c r="G93" s="42"/>
-    </row>
-    <row r="94" s="36" customFormat="1"/>
-    <row r="95" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A95" s="41"/>
-      <c r="B95" s="42"/>
-      <c r="C95" s="42"/>
-      <c r="D95" s="42"/>
-      <c r="E95" s="42"/>
-      <c r="F95" s="42"/>
-      <c r="G95" s="42"/>
-    </row>
-    <row r="96" s="36" customFormat="1"/>
-    <row r="97" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A97" s="41"/>
-      <c r="B97" s="42"/>
-      <c r="C97" s="42"/>
-      <c r="D97" s="42"/>
-      <c r="E97" s="42"/>
-      <c r="F97" s="42"/>
-      <c r="G97" s="42"/>
-    </row>
-    <row r="98" s="36" customFormat="1"/>
-    <row r="99" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A99" s="41"/>
-      <c r="B99" s="42"/>
-      <c r="C99" s="42"/>
-      <c r="D99" s="42"/>
-      <c r="E99" s="42"/>
-      <c r="F99" s="42"/>
-      <c r="G99" s="42"/>
-    </row>
-    <row r="100" s="36" customFormat="1"/>
-    <row r="101" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A101" s="41"/>
-      <c r="B101" s="42"/>
-      <c r="C101" s="42"/>
-      <c r="D101" s="42"/>
-      <c r="E101" s="42"/>
-      <c r="F101" s="42"/>
-      <c r="G101" s="42"/>
-    </row>
-    <row r="102" s="36" customFormat="1"/>
-    <row r="103" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A103" s="41"/>
-      <c r="B103" s="42"/>
-      <c r="C103" s="42"/>
-      <c r="D103" s="42"/>
-      <c r="E103" s="42"/>
-      <c r="F103" s="42"/>
-      <c r="G103" s="42"/>
-    </row>
-    <row r="104" s="36" customFormat="1"/>
-    <row r="105" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A105" s="41"/>
-      <c r="B105" s="42"/>
-      <c r="C105" s="42"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="42"/>
-      <c r="F105" s="42"/>
-      <c r="G105" s="42"/>
-    </row>
-    <row r="106" s="36" customFormat="1"/>
-    <row r="107" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A107" s="41"/>
-      <c r="B107" s="42"/>
-      <c r="C107" s="42"/>
-      <c r="D107" s="42"/>
-      <c r="E107" s="42"/>
-      <c r="F107" s="42"/>
-      <c r="G107" s="42"/>
-    </row>
-    <row r="108" s="36" customFormat="1"/>
-    <row r="109" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A109" s="41"/>
-      <c r="B109" s="42"/>
-      <c r="C109" s="42"/>
-      <c r="D109" s="42"/>
-      <c r="E109" s="42"/>
-      <c r="F109" s="42"/>
-      <c r="G109" s="42"/>
-    </row>
-    <row r="110" s="36" customFormat="1"/>
-    <row r="111" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A111" s="41"/>
-      <c r="B111" s="42"/>
-      <c r="C111" s="42"/>
-      <c r="D111" s="42"/>
-      <c r="E111" s="42"/>
-      <c r="F111" s="42"/>
-      <c r="G111" s="42"/>
-    </row>
-    <row r="112" s="36" customFormat="1"/>
-    <row r="113" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A113" s="41"/>
-      <c r="B113" s="42"/>
-      <c r="C113" s="42"/>
-      <c r="D113" s="42"/>
-      <c r="E113" s="42"/>
-      <c r="F113" s="42"/>
-      <c r="G113" s="42"/>
-    </row>
-    <row r="114" s="36" customFormat="1"/>
-    <row r="115" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A115" s="41"/>
-      <c r="B115" s="42"/>
-      <c r="C115" s="42"/>
-      <c r="D115" s="42"/>
-      <c r="E115" s="42"/>
-      <c r="F115" s="42"/>
-      <c r="G115" s="42"/>
-    </row>
-    <row r="116" s="36" customFormat="1"/>
-    <row r="117" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A117" s="41"/>
-      <c r="B117" s="42"/>
-      <c r="C117" s="42"/>
-      <c r="D117" s="42"/>
-      <c r="E117" s="42"/>
-      <c r="F117" s="42"/>
-      <c r="G117" s="42"/>
-    </row>
-    <row r="118" s="36" customFormat="1"/>
-    <row r="119" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A119" s="41"/>
-      <c r="B119" s="42"/>
-      <c r="C119" s="42"/>
-      <c r="D119" s="42"/>
-      <c r="E119" s="42"/>
-      <c r="F119" s="42"/>
-      <c r="G119" s="42"/>
-    </row>
-    <row r="120" s="36" customFormat="1"/>
-    <row r="121" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A121" s="41"/>
-      <c r="B121" s="42"/>
-      <c r="C121" s="42"/>
-      <c r="D121" s="42"/>
-      <c r="E121" s="42"/>
-      <c r="F121" s="42"/>
-      <c r="G121" s="42"/>
-    </row>
-    <row r="122" s="36" customFormat="1"/>
-    <row r="123" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A123" s="41"/>
-      <c r="B123" s="42"/>
-      <c r="C123" s="42"/>
-      <c r="D123" s="42"/>
-      <c r="E123" s="42"/>
-      <c r="F123" s="42"/>
-      <c r="G123" s="42"/>
-    </row>
-    <row r="124" s="36" customFormat="1"/>
-    <row r="125" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A125" s="41"/>
-      <c r="B125" s="42"/>
-      <c r="C125" s="42"/>
-      <c r="D125" s="42"/>
-      <c r="E125" s="42"/>
-      <c r="F125" s="42"/>
-      <c r="G125" s="42"/>
-    </row>
-    <row r="126" s="36" customFormat="1"/>
-    <row r="127" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A127" s="41"/>
-      <c r="B127" s="42"/>
-      <c r="C127" s="42"/>
-      <c r="D127" s="42"/>
-      <c r="E127" s="42"/>
-      <c r="F127" s="42"/>
-      <c r="G127" s="42"/>
-    </row>
-    <row r="128" s="36" customFormat="1"/>
-    <row r="129" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A129" s="41"/>
-      <c r="B129" s="42"/>
-      <c r="C129" s="42"/>
-      <c r="D129" s="42"/>
-      <c r="E129" s="42"/>
-      <c r="F129" s="42"/>
-      <c r="G129" s="42"/>
-    </row>
-    <row r="130" s="36" customFormat="1"/>
-    <row r="131" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A131" s="41"/>
-      <c r="B131" s="42"/>
-      <c r="C131" s="42"/>
-      <c r="D131" s="42"/>
-      <c r="E131" s="42"/>
-      <c r="F131" s="42"/>
-      <c r="G131" s="42"/>
-    </row>
-    <row r="132" s="36" customFormat="1"/>
-    <row r="133" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A133" s="41"/>
-      <c r="B133" s="42"/>
-      <c r="C133" s="42"/>
-      <c r="D133" s="42"/>
-      <c r="E133" s="42"/>
-      <c r="F133" s="42"/>
-      <c r="G133" s="42"/>
-    </row>
-    <row r="134" s="36" customFormat="1"/>
-    <row r="135" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A135" s="41"/>
-      <c r="B135" s="42"/>
-      <c r="C135" s="42"/>
-      <c r="D135" s="42"/>
-      <c r="E135" s="42"/>
-      <c r="F135" s="42"/>
-      <c r="G135" s="42"/>
-    </row>
-    <row r="136" s="36" customFormat="1"/>
-    <row r="137" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A137" s="41"/>
-      <c r="B137" s="42"/>
-      <c r="C137" s="42"/>
-      <c r="D137" s="42"/>
-      <c r="E137" s="42"/>
-      <c r="F137" s="42"/>
-      <c r="G137" s="42"/>
-    </row>
-    <row r="138" s="36" customFormat="1"/>
-    <row r="139" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A139" s="41"/>
-      <c r="B139" s="42"/>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="42"/>
-      <c r="G139" s="42"/>
-    </row>
-    <row r="140" s="36" customFormat="1"/>
-    <row r="141" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A141" s="41"/>
-      <c r="B141" s="42"/>
-      <c r="C141" s="42"/>
-      <c r="D141" s="42"/>
-      <c r="E141" s="42"/>
-      <c r="F141" s="42"/>
-      <c r="G141" s="42"/>
-    </row>
-    <row r="142" s="36" customFormat="1"/>
-    <row r="143" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A143" s="41"/>
-      <c r="B143" s="42"/>
-      <c r="C143" s="42"/>
-      <c r="D143" s="42"/>
-      <c r="E143" s="42"/>
-      <c r="F143" s="42"/>
-      <c r="G143" s="42"/>
-    </row>
-    <row r="144" s="36" customFormat="1"/>
-    <row r="145" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A145" s="41"/>
-      <c r="B145" s="42"/>
-      <c r="C145" s="42"/>
-      <c r="D145" s="42"/>
-      <c r="E145" s="42"/>
-      <c r="F145" s="42"/>
-      <c r="G145" s="42"/>
-    </row>
-    <row r="146" s="36" customFormat="1"/>
-    <row r="147" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A147" s="41"/>
-      <c r="B147" s="42"/>
-      <c r="C147" s="42"/>
-      <c r="D147" s="42"/>
-      <c r="E147" s="42"/>
-      <c r="F147" s="42"/>
-      <c r="G147" s="42"/>
-    </row>
-    <row r="148" s="36" customFormat="1"/>
-    <row r="149" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A149" s="41"/>
-      <c r="B149" s="42"/>
-      <c r="C149" s="42"/>
-      <c r="D149" s="42"/>
-      <c r="E149" s="42"/>
-      <c r="F149" s="42"/>
-      <c r="G149" s="42"/>
-    </row>
-    <row r="150" s="36" customFormat="1"/>
-    <row r="151" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A151" s="41"/>
-      <c r="B151" s="42"/>
-      <c r="C151" s="42"/>
-      <c r="D151" s="42"/>
-      <c r="E151" s="42"/>
-      <c r="F151" s="42"/>
-      <c r="G151" s="42"/>
-    </row>
-    <row r="152" s="36" customFormat="1"/>
-    <row r="153" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A153" s="41"/>
-      <c r="B153" s="42"/>
-      <c r="C153" s="42"/>
-      <c r="D153" s="42"/>
-      <c r="E153" s="42"/>
-      <c r="F153" s="42"/>
-      <c r="G153" s="42"/>
-    </row>
-    <row r="154" s="36" customFormat="1"/>
-    <row r="155" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A155" s="41"/>
-      <c r="B155" s="42"/>
-      <c r="C155" s="42"/>
-      <c r="D155" s="42"/>
-      <c r="E155" s="42"/>
-      <c r="F155" s="42"/>
-      <c r="G155" s="42"/>
-    </row>
-    <row r="156" s="36" customFormat="1"/>
-    <row r="157" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A157" s="41"/>
-      <c r="B157" s="42"/>
-      <c r="C157" s="42"/>
-      <c r="D157" s="42"/>
-      <c r="E157" s="42"/>
-      <c r="F157" s="42"/>
-      <c r="G157" s="42"/>
-    </row>
-    <row r="158" s="36" customFormat="1"/>
-    <row r="159" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A159" s="41"/>
-      <c r="B159" s="42"/>
-      <c r="C159" s="42"/>
-      <c r="D159" s="42"/>
-      <c r="E159" s="42"/>
-      <c r="F159" s="42"/>
-      <c r="G159" s="42"/>
-    </row>
-    <row r="160" s="36" customFormat="1"/>
-    <row r="161" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A161" s="41"/>
-      <c r="B161" s="42"/>
-      <c r="C161" s="42"/>
-      <c r="D161" s="42"/>
-      <c r="E161" s="42"/>
-      <c r="F161" s="42"/>
-      <c r="G161" s="42"/>
-    </row>
-    <row r="162" s="36" customFormat="1"/>
-    <row r="163" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A163" s="41"/>
-      <c r="B163" s="42"/>
-      <c r="C163" s="42"/>
-      <c r="D163" s="42"/>
-      <c r="E163" s="42"/>
-      <c r="F163" s="42"/>
-      <c r="G163" s="42"/>
-    </row>
-    <row r="164" s="36" customFormat="1"/>
-    <row r="165" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A165" s="41"/>
-      <c r="B165" s="42"/>
-      <c r="C165" s="42"/>
-      <c r="D165" s="42"/>
-      <c r="E165" s="42"/>
-      <c r="F165" s="42"/>
-      <c r="G165" s="42"/>
-    </row>
-    <row r="166" s="36" customFormat="1"/>
-    <row r="167" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A167" s="41"/>
-      <c r="B167" s="42"/>
-      <c r="C167" s="42"/>
-      <c r="D167" s="42"/>
-      <c r="E167" s="42"/>
-      <c r="F167" s="42"/>
-      <c r="G167" s="42"/>
-    </row>
-    <row r="168" s="36" customFormat="1"/>
-    <row r="169" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A169" s="41"/>
-      <c r="B169" s="42"/>
-      <c r="C169" s="42"/>
-      <c r="D169" s="42"/>
-      <c r="E169" s="42"/>
-      <c r="F169" s="42"/>
-      <c r="G169" s="42"/>
-    </row>
-    <row r="170" s="36" customFormat="1"/>
-    <row r="171" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A171" s="41"/>
-      <c r="B171" s="42"/>
-      <c r="C171" s="42"/>
-      <c r="D171" s="42"/>
-      <c r="E171" s="42"/>
-      <c r="F171" s="42"/>
-      <c r="G171" s="42"/>
-    </row>
-    <row r="172" s="36" customFormat="1"/>
-    <row r="173" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A173" s="41"/>
-      <c r="B173" s="42"/>
-      <c r="C173" s="42"/>
-      <c r="D173" s="42"/>
-      <c r="E173" s="42"/>
-      <c r="F173" s="42"/>
-      <c r="G173" s="42"/>
-    </row>
-    <row r="174" s="36" customFormat="1"/>
-    <row r="175" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A175" s="41"/>
-      <c r="B175" s="42"/>
-      <c r="C175" s="42"/>
-      <c r="D175" s="42"/>
-      <c r="E175" s="42"/>
-      <c r="F175" s="42"/>
-      <c r="G175" s="42"/>
-    </row>
-    <row r="176" s="36" customFormat="1"/>
-    <row r="177" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A177" s="41"/>
-      <c r="B177" s="42"/>
-      <c r="C177" s="42"/>
-      <c r="D177" s="42"/>
-      <c r="E177" s="42"/>
-      <c r="F177" s="42"/>
-      <c r="G177" s="42"/>
-    </row>
-    <row r="178" s="36" customFormat="1"/>
-    <row r="179" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A179" s="41"/>
-      <c r="B179" s="42"/>
-      <c r="C179" s="42"/>
-      <c r="D179" s="42"/>
-      <c r="E179" s="42"/>
-      <c r="F179" s="42"/>
-      <c r="G179" s="42"/>
-    </row>
-    <row r="180" s="36" customFormat="1"/>
-    <row r="181" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A181" s="41"/>
-      <c r="B181" s="42"/>
-      <c r="C181" s="42"/>
-      <c r="D181" s="42"/>
-      <c r="E181" s="42"/>
-      <c r="F181" s="42"/>
-      <c r="G181" s="42"/>
-    </row>
-    <row r="182" s="36" customFormat="1"/>
-    <row r="183" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A183" s="41"/>
-      <c r="B183" s="42"/>
-      <c r="C183" s="42"/>
-      <c r="D183" s="42"/>
-      <c r="E183" s="42"/>
-      <c r="F183" s="42"/>
-      <c r="G183" s="42"/>
-    </row>
-    <row r="184" s="36" customFormat="1"/>
-    <row r="185" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A185" s="41"/>
-      <c r="B185" s="42"/>
-      <c r="C185" s="42"/>
-      <c r="D185" s="42"/>
-      <c r="E185" s="42"/>
-      <c r="F185" s="42"/>
-      <c r="G185" s="42"/>
-    </row>
-    <row r="186" s="36" customFormat="1"/>
-    <row r="187" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A187" s="41"/>
-      <c r="B187" s="42"/>
-      <c r="C187" s="42"/>
-      <c r="D187" s="42"/>
-      <c r="E187" s="42"/>
-      <c r="F187" s="42"/>
-      <c r="G187" s="42"/>
-    </row>
-    <row r="188" s="36" customFormat="1"/>
-    <row r="189" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A189" s="41"/>
-      <c r="B189" s="42"/>
-      <c r="C189" s="42"/>
-      <c r="D189" s="42"/>
-      <c r="E189" s="42"/>
-      <c r="F189" s="42"/>
-      <c r="G189" s="42"/>
-    </row>
-    <row r="190" s="36" customFormat="1"/>
-    <row r="191" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A191" s="41"/>
-      <c r="B191" s="42"/>
-      <c r="C191" s="42"/>
-      <c r="D191" s="42"/>
-      <c r="E191" s="42"/>
-      <c r="F191" s="42"/>
-      <c r="G191" s="42"/>
-    </row>
-    <row r="192" s="36" customFormat="1"/>
-    <row r="193" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A193" s="41"/>
-      <c r="B193" s="42"/>
-      <c r="C193" s="42"/>
-      <c r="D193" s="42"/>
-      <c r="E193" s="42"/>
-      <c r="F193" s="42"/>
-      <c r="G193" s="42"/>
-    </row>
-    <row r="194" s="36" customFormat="1"/>
-    <row r="195" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A195" s="41"/>
-      <c r="B195" s="42"/>
-      <c r="C195" s="42"/>
-      <c r="D195" s="42"/>
-      <c r="E195" s="42"/>
-      <c r="F195" s="42"/>
-      <c r="G195" s="42"/>
-    </row>
-    <row r="196" s="36" customFormat="1"/>
-    <row r="197" s="36" customFormat="1" ht="13.85" spans="1:7">
-      <c r="A197" s="41"/>
-      <c r="B197" s="42"/>
-      <c r="C197" s="42"/>
-      <c r="D197" s="42"/>
-      <c r="E197" s="42"/>
-      <c r="F197" s="42"/>
-      <c r="G197" s="42"/>
+    <row r="7" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A7" s="48"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+    </row>
+    <row r="8" s="43" customFormat="1"/>
+    <row r="9" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+    </row>
+    <row r="10" s="43" customFormat="1"/>
+    <row r="11" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+    </row>
+    <row r="12" s="43" customFormat="1"/>
+    <row r="13" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+    </row>
+    <row r="14" s="43" customFormat="1"/>
+    <row r="15" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+    </row>
+    <row r="16" s="43" customFormat="1"/>
+    <row r="17" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+    </row>
+    <row r="18" s="43" customFormat="1"/>
+    <row r="19" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A19" s="48"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+    </row>
+    <row r="20" s="43" customFormat="1"/>
+    <row r="21" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+    </row>
+    <row r="22" s="43" customFormat="1"/>
+    <row r="23" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A23" s="48"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+    </row>
+    <row r="24" s="43" customFormat="1"/>
+    <row r="25" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A25" s="48"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+    </row>
+    <row r="26" s="43" customFormat="1"/>
+    <row r="27" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A27" s="48"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+    </row>
+    <row r="28" s="43" customFormat="1"/>
+    <row r="29" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A29" s="48"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+    </row>
+    <row r="30" s="43" customFormat="1"/>
+    <row r="31" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A31" s="48"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+    </row>
+    <row r="32" s="43" customFormat="1"/>
+    <row r="33" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A33" s="48"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+    </row>
+    <row r="34" s="43" customFormat="1"/>
+    <row r="35" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A35" s="48"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+    </row>
+    <row r="36" s="43" customFormat="1"/>
+    <row r="37" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A37" s="48"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+    </row>
+    <row r="38" s="43" customFormat="1"/>
+    <row r="39" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A39" s="48"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+    </row>
+    <row r="40" s="43" customFormat="1"/>
+    <row r="41" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A41" s="48"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+    </row>
+    <row r="42" s="43" customFormat="1"/>
+    <row r="43" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A43" s="48"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+    </row>
+    <row r="44" s="43" customFormat="1"/>
+    <row r="45" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A45" s="48"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+    </row>
+    <row r="46" s="43" customFormat="1"/>
+    <row r="47" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A47" s="48"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
+    </row>
+    <row r="48" s="43" customFormat="1"/>
+    <row r="49" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A49" s="48"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+    </row>
+    <row r="50" s="43" customFormat="1"/>
+    <row r="51" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A51" s="48"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+    </row>
+    <row r="52" s="43" customFormat="1"/>
+    <row r="53" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A53" s="48"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
+    </row>
+    <row r="54" s="43" customFormat="1"/>
+    <row r="55" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A55" s="48"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+    </row>
+    <row r="56" s="43" customFormat="1"/>
+    <row r="57" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A57" s="48"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+    </row>
+    <row r="58" s="43" customFormat="1"/>
+    <row r="59" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A59" s="48"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+    </row>
+    <row r="60" s="43" customFormat="1"/>
+    <row r="61" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A61" s="48"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49"/>
+    </row>
+    <row r="62" s="43" customFormat="1"/>
+    <row r="63" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A63" s="48"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+    </row>
+    <row r="64" s="43" customFormat="1"/>
+    <row r="65" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A65" s="48"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="49"/>
+    </row>
+    <row r="66" s="43" customFormat="1"/>
+    <row r="67" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A67" s="48"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49"/>
+    </row>
+    <row r="68" s="43" customFormat="1"/>
+    <row r="69" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A69" s="48"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+    </row>
+    <row r="70" s="43" customFormat="1"/>
+    <row r="71" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A71" s="48"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+    </row>
+    <row r="72" s="43" customFormat="1"/>
+    <row r="73" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A73" s="48"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+    </row>
+    <row r="74" s="43" customFormat="1"/>
+    <row r="75" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A75" s="48"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+    </row>
+    <row r="76" s="43" customFormat="1"/>
+    <row r="77" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A77" s="48"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="49"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+    </row>
+    <row r="78" s="43" customFormat="1"/>
+    <row r="79" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A79" s="48"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+    </row>
+    <row r="80" s="43" customFormat="1"/>
+    <row r="81" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A81" s="48"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
+    </row>
+    <row r="82" s="43" customFormat="1"/>
+    <row r="83" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A83" s="48"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="49"/>
+    </row>
+    <row r="84" s="43" customFormat="1"/>
+    <row r="85" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A85" s="48"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="49"/>
+      <c r="D85" s="49"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
+    </row>
+    <row r="86" s="43" customFormat="1"/>
+    <row r="87" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A87" s="48"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
+    </row>
+    <row r="88" s="43" customFormat="1"/>
+    <row r="89" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A89" s="48"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
+      <c r="D89" s="49"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="49"/>
+      <c r="G89" s="49"/>
+    </row>
+    <row r="90" s="43" customFormat="1"/>
+    <row r="91" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A91" s="48"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="49"/>
+      <c r="E91" s="49"/>
+      <c r="F91" s="49"/>
+      <c r="G91" s="49"/>
+    </row>
+    <row r="92" s="43" customFormat="1"/>
+    <row r="93" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A93" s="48"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="49"/>
+      <c r="D93" s="49"/>
+      <c r="E93" s="49"/>
+      <c r="F93" s="49"/>
+      <c r="G93" s="49"/>
+    </row>
+    <row r="94" s="43" customFormat="1"/>
+    <row r="95" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A95" s="48"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49"/>
+      <c r="D95" s="49"/>
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
+    </row>
+    <row r="96" s="43" customFormat="1"/>
+    <row r="97" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A97" s="48"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="49"/>
+      <c r="D97" s="49"/>
+      <c r="E97" s="49"/>
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
+    </row>
+    <row r="98" s="43" customFormat="1"/>
+    <row r="99" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A99" s="48"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
+    </row>
+    <row r="100" s="43" customFormat="1"/>
+    <row r="101" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A101" s="48"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="49"/>
+      <c r="D101" s="49"/>
+      <c r="E101" s="49"/>
+      <c r="F101" s="49"/>
+      <c r="G101" s="49"/>
+    </row>
+    <row r="102" s="43" customFormat="1"/>
+    <row r="103" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A103" s="48"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="49"/>
+      <c r="D103" s="49"/>
+      <c r="E103" s="49"/>
+      <c r="F103" s="49"/>
+      <c r="G103" s="49"/>
+    </row>
+    <row r="104" s="43" customFormat="1"/>
+    <row r="105" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A105" s="48"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="49"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="49"/>
+    </row>
+    <row r="106" s="43" customFormat="1"/>
+    <row r="107" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A107" s="48"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="49"/>
+    </row>
+    <row r="108" s="43" customFormat="1"/>
+    <row r="109" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A109" s="48"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="49"/>
+    </row>
+    <row r="110" s="43" customFormat="1"/>
+    <row r="111" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A111" s="48"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
+    </row>
+    <row r="112" s="43" customFormat="1"/>
+    <row r="113" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A113" s="48"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="49"/>
+      <c r="D113" s="49"/>
+      <c r="E113" s="49"/>
+      <c r="F113" s="49"/>
+      <c r="G113" s="49"/>
+    </row>
+    <row r="114" s="43" customFormat="1"/>
+    <row r="115" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A115" s="48"/>
+      <c r="B115" s="49"/>
+      <c r="C115" s="49"/>
+      <c r="D115" s="49"/>
+      <c r="E115" s="49"/>
+      <c r="F115" s="49"/>
+      <c r="G115" s="49"/>
+    </row>
+    <row r="116" s="43" customFormat="1"/>
+    <row r="117" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A117" s="48"/>
+      <c r="B117" s="49"/>
+      <c r="C117" s="49"/>
+      <c r="D117" s="49"/>
+      <c r="E117" s="49"/>
+      <c r="F117" s="49"/>
+      <c r="G117" s="49"/>
+    </row>
+    <row r="118" s="43" customFormat="1"/>
+    <row r="119" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A119" s="48"/>
+      <c r="B119" s="49"/>
+      <c r="C119" s="49"/>
+      <c r="D119" s="49"/>
+      <c r="E119" s="49"/>
+      <c r="F119" s="49"/>
+      <c r="G119" s="49"/>
+    </row>
+    <row r="120" s="43" customFormat="1"/>
+    <row r="121" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A121" s="48"/>
+      <c r="B121" s="49"/>
+      <c r="C121" s="49"/>
+      <c r="D121" s="49"/>
+      <c r="E121" s="49"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="49"/>
+    </row>
+    <row r="122" s="43" customFormat="1"/>
+    <row r="123" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A123" s="48"/>
+      <c r="B123" s="49"/>
+      <c r="C123" s="49"/>
+      <c r="D123" s="49"/>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="49"/>
+    </row>
+    <row r="124" s="43" customFormat="1"/>
+    <row r="125" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A125" s="48"/>
+      <c r="B125" s="49"/>
+      <c r="C125" s="49"/>
+      <c r="D125" s="49"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="49"/>
+    </row>
+    <row r="126" s="43" customFormat="1"/>
+    <row r="127" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A127" s="48"/>
+      <c r="B127" s="49"/>
+      <c r="C127" s="49"/>
+      <c r="D127" s="49"/>
+      <c r="E127" s="49"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="49"/>
+    </row>
+    <row r="128" s="43" customFormat="1"/>
+    <row r="129" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A129" s="48"/>
+      <c r="B129" s="49"/>
+      <c r="C129" s="49"/>
+      <c r="D129" s="49"/>
+      <c r="E129" s="49"/>
+      <c r="F129" s="49"/>
+      <c r="G129" s="49"/>
+    </row>
+    <row r="130" s="43" customFormat="1"/>
+    <row r="131" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A131" s="48"/>
+      <c r="B131" s="49"/>
+      <c r="C131" s="49"/>
+      <c r="D131" s="49"/>
+      <c r="E131" s="49"/>
+      <c r="F131" s="49"/>
+      <c r="G131" s="49"/>
+    </row>
+    <row r="132" s="43" customFormat="1"/>
+    <row r="133" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A133" s="48"/>
+      <c r="B133" s="49"/>
+      <c r="C133" s="49"/>
+      <c r="D133" s="49"/>
+      <c r="E133" s="49"/>
+      <c r="F133" s="49"/>
+      <c r="G133" s="49"/>
+    </row>
+    <row r="134" s="43" customFormat="1"/>
+    <row r="135" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A135" s="48"/>
+      <c r="B135" s="49"/>
+      <c r="C135" s="49"/>
+      <c r="D135" s="49"/>
+      <c r="E135" s="49"/>
+      <c r="F135" s="49"/>
+      <c r="G135" s="49"/>
+    </row>
+    <row r="136" s="43" customFormat="1"/>
+    <row r="137" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A137" s="48"/>
+      <c r="B137" s="49"/>
+      <c r="C137" s="49"/>
+      <c r="D137" s="49"/>
+      <c r="E137" s="49"/>
+      <c r="F137" s="49"/>
+      <c r="G137" s="49"/>
+    </row>
+    <row r="138" s="43" customFormat="1"/>
+    <row r="139" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A139" s="48"/>
+      <c r="B139" s="49"/>
+      <c r="C139" s="49"/>
+      <c r="D139" s="49"/>
+      <c r="E139" s="49"/>
+      <c r="F139" s="49"/>
+      <c r="G139" s="49"/>
+    </row>
+    <row r="140" s="43" customFormat="1"/>
+    <row r="141" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A141" s="48"/>
+      <c r="B141" s="49"/>
+      <c r="C141" s="49"/>
+      <c r="D141" s="49"/>
+      <c r="E141" s="49"/>
+      <c r="F141" s="49"/>
+      <c r="G141" s="49"/>
+    </row>
+    <row r="142" s="43" customFormat="1"/>
+    <row r="143" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A143" s="48"/>
+      <c r="B143" s="49"/>
+      <c r="C143" s="49"/>
+      <c r="D143" s="49"/>
+      <c r="E143" s="49"/>
+      <c r="F143" s="49"/>
+      <c r="G143" s="49"/>
+    </row>
+    <row r="144" s="43" customFormat="1"/>
+    <row r="145" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A145" s="48"/>
+      <c r="B145" s="49"/>
+      <c r="C145" s="49"/>
+      <c r="D145" s="49"/>
+      <c r="E145" s="49"/>
+      <c r="F145" s="49"/>
+      <c r="G145" s="49"/>
+    </row>
+    <row r="146" s="43" customFormat="1"/>
+    <row r="147" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A147" s="48"/>
+      <c r="B147" s="49"/>
+      <c r="C147" s="49"/>
+      <c r="D147" s="49"/>
+      <c r="E147" s="49"/>
+      <c r="F147" s="49"/>
+      <c r="G147" s="49"/>
+    </row>
+    <row r="148" s="43" customFormat="1"/>
+    <row r="149" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A149" s="48"/>
+      <c r="B149" s="49"/>
+      <c r="C149" s="49"/>
+      <c r="D149" s="49"/>
+      <c r="E149" s="49"/>
+      <c r="F149" s="49"/>
+      <c r="G149" s="49"/>
+    </row>
+    <row r="150" s="43" customFormat="1"/>
+    <row r="151" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A151" s="48"/>
+      <c r="B151" s="49"/>
+      <c r="C151" s="49"/>
+      <c r="D151" s="49"/>
+      <c r="E151" s="49"/>
+      <c r="F151" s="49"/>
+      <c r="G151" s="49"/>
+    </row>
+    <row r="152" s="43" customFormat="1"/>
+    <row r="153" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A153" s="48"/>
+      <c r="B153" s="49"/>
+      <c r="C153" s="49"/>
+      <c r="D153" s="49"/>
+      <c r="E153" s="49"/>
+      <c r="F153" s="49"/>
+      <c r="G153" s="49"/>
+    </row>
+    <row r="154" s="43" customFormat="1"/>
+    <row r="155" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A155" s="48"/>
+      <c r="B155" s="49"/>
+      <c r="C155" s="49"/>
+      <c r="D155" s="49"/>
+      <c r="E155" s="49"/>
+      <c r="F155" s="49"/>
+      <c r="G155" s="49"/>
+    </row>
+    <row r="156" s="43" customFormat="1"/>
+    <row r="157" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A157" s="48"/>
+      <c r="B157" s="49"/>
+      <c r="C157" s="49"/>
+      <c r="D157" s="49"/>
+      <c r="E157" s="49"/>
+      <c r="F157" s="49"/>
+      <c r="G157" s="49"/>
+    </row>
+    <row r="158" s="43" customFormat="1"/>
+    <row r="159" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A159" s="48"/>
+      <c r="B159" s="49"/>
+      <c r="C159" s="49"/>
+      <c r="D159" s="49"/>
+      <c r="E159" s="49"/>
+      <c r="F159" s="49"/>
+      <c r="G159" s="49"/>
+    </row>
+    <row r="160" s="43" customFormat="1"/>
+    <row r="161" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A161" s="48"/>
+      <c r="B161" s="49"/>
+      <c r="C161" s="49"/>
+      <c r="D161" s="49"/>
+      <c r="E161" s="49"/>
+      <c r="F161" s="49"/>
+      <c r="G161" s="49"/>
+    </row>
+    <row r="162" s="43" customFormat="1"/>
+    <row r="163" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A163" s="48"/>
+      <c r="B163" s="49"/>
+      <c r="C163" s="49"/>
+      <c r="D163" s="49"/>
+      <c r="E163" s="49"/>
+      <c r="F163" s="49"/>
+      <c r="G163" s="49"/>
+    </row>
+    <row r="164" s="43" customFormat="1"/>
+    <row r="165" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A165" s="48"/>
+      <c r="B165" s="49"/>
+      <c r="C165" s="49"/>
+      <c r="D165" s="49"/>
+      <c r="E165" s="49"/>
+      <c r="F165" s="49"/>
+      <c r="G165" s="49"/>
+    </row>
+    <row r="166" s="43" customFormat="1"/>
+    <row r="167" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A167" s="48"/>
+      <c r="B167" s="49"/>
+      <c r="C167" s="49"/>
+      <c r="D167" s="49"/>
+      <c r="E167" s="49"/>
+      <c r="F167" s="49"/>
+      <c r="G167" s="49"/>
+    </row>
+    <row r="168" s="43" customFormat="1"/>
+    <row r="169" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A169" s="48"/>
+      <c r="B169" s="49"/>
+      <c r="C169" s="49"/>
+      <c r="D169" s="49"/>
+      <c r="E169" s="49"/>
+      <c r="F169" s="49"/>
+      <c r="G169" s="49"/>
+    </row>
+    <row r="170" s="43" customFormat="1"/>
+    <row r="171" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A171" s="48"/>
+      <c r="B171" s="49"/>
+      <c r="C171" s="49"/>
+      <c r="D171" s="49"/>
+      <c r="E171" s="49"/>
+      <c r="F171" s="49"/>
+      <c r="G171" s="49"/>
+    </row>
+    <row r="172" s="43" customFormat="1"/>
+    <row r="173" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A173" s="48"/>
+      <c r="B173" s="49"/>
+      <c r="C173" s="49"/>
+      <c r="D173" s="49"/>
+      <c r="E173" s="49"/>
+      <c r="F173" s="49"/>
+      <c r="G173" s="49"/>
+    </row>
+    <row r="174" s="43" customFormat="1"/>
+    <row r="175" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A175" s="48"/>
+      <c r="B175" s="49"/>
+      <c r="C175" s="49"/>
+      <c r="D175" s="49"/>
+      <c r="E175" s="49"/>
+      <c r="F175" s="49"/>
+      <c r="G175" s="49"/>
+    </row>
+    <row r="176" s="43" customFormat="1"/>
+    <row r="177" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A177" s="48"/>
+      <c r="B177" s="49"/>
+      <c r="C177" s="49"/>
+      <c r="D177" s="49"/>
+      <c r="E177" s="49"/>
+      <c r="F177" s="49"/>
+      <c r="G177" s="49"/>
+    </row>
+    <row r="178" s="43" customFormat="1"/>
+    <row r="179" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A179" s="48"/>
+      <c r="B179" s="49"/>
+      <c r="C179" s="49"/>
+      <c r="D179" s="49"/>
+      <c r="E179" s="49"/>
+      <c r="F179" s="49"/>
+      <c r="G179" s="49"/>
+    </row>
+    <row r="180" s="43" customFormat="1"/>
+    <row r="181" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A181" s="48"/>
+      <c r="B181" s="49"/>
+      <c r="C181" s="49"/>
+      <c r="D181" s="49"/>
+      <c r="E181" s="49"/>
+      <c r="F181" s="49"/>
+      <c r="G181" s="49"/>
+    </row>
+    <row r="182" s="43" customFormat="1"/>
+    <row r="183" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A183" s="48"/>
+      <c r="B183" s="49"/>
+      <c r="C183" s="49"/>
+      <c r="D183" s="49"/>
+      <c r="E183" s="49"/>
+      <c r="F183" s="49"/>
+      <c r="G183" s="49"/>
+    </row>
+    <row r="184" s="43" customFormat="1"/>
+    <row r="185" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A185" s="48"/>
+      <c r="B185" s="49"/>
+      <c r="C185" s="49"/>
+      <c r="D185" s="49"/>
+      <c r="E185" s="49"/>
+      <c r="F185" s="49"/>
+      <c r="G185" s="49"/>
+    </row>
+    <row r="186" s="43" customFormat="1"/>
+    <row r="187" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A187" s="48"/>
+      <c r="B187" s="49"/>
+      <c r="C187" s="49"/>
+      <c r="D187" s="49"/>
+      <c r="E187" s="49"/>
+      <c r="F187" s="49"/>
+      <c r="G187" s="49"/>
+    </row>
+    <row r="188" s="43" customFormat="1"/>
+    <row r="189" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A189" s="48"/>
+      <c r="B189" s="49"/>
+      <c r="C189" s="49"/>
+      <c r="D189" s="49"/>
+      <c r="E189" s="49"/>
+      <c r="F189" s="49"/>
+      <c r="G189" s="49"/>
+    </row>
+    <row r="190" s="43" customFormat="1"/>
+    <row r="191" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A191" s="48"/>
+      <c r="B191" s="49"/>
+      <c r="C191" s="49"/>
+      <c r="D191" s="49"/>
+      <c r="E191" s="49"/>
+      <c r="F191" s="49"/>
+      <c r="G191" s="49"/>
+    </row>
+    <row r="192" s="43" customFormat="1"/>
+    <row r="193" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A193" s="48"/>
+      <c r="B193" s="49"/>
+      <c r="C193" s="49"/>
+      <c r="D193" s="49"/>
+      <c r="E193" s="49"/>
+      <c r="F193" s="49"/>
+      <c r="G193" s="49"/>
+    </row>
+    <row r="194" s="43" customFormat="1"/>
+    <row r="195" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A195" s="48"/>
+      <c r="B195" s="49"/>
+      <c r="C195" s="49"/>
+      <c r="D195" s="49"/>
+      <c r="E195" s="49"/>
+      <c r="F195" s="49"/>
+      <c r="G195" s="49"/>
+    </row>
+    <row r="196" s="43" customFormat="1"/>
+    <row r="197" s="43" customFormat="1" ht="13.85" spans="1:7">
+      <c r="A197" s="48"/>
+      <c r="B197" s="49"/>
+      <c r="C197" s="49"/>
+      <c r="D197" s="49"/>
+      <c r="E197" s="49"/>
+      <c r="F197" s="49"/>
+      <c r="G197" s="49"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:G25" etc:filterBottomFollowUsedRange="0">
@@ -3096,12 +3336,12 @@
   <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.6637168141593" style="24" customWidth="1"/>
-    <col min="2" max="2" width="23.2212389380531" style="25" customWidth="1"/>
-    <col min="3" max="3" width="29.4424778761062" style="25" customWidth="1"/>
+    <col min="1" max="1" width="14.6637168141593" style="31" customWidth="1"/>
+    <col min="2" max="2" width="23.2212389380531" style="32" customWidth="1"/>
+    <col min="3" max="3" width="29.4424778761062" style="32" customWidth="1"/>
     <col min="4" max="4" width="38.2212389380531" customWidth="1"/>
     <col min="5" max="5" width="22.5575221238938" customWidth="1"/>
-    <col min="6" max="6" width="16.3362831858407" style="26"/>
+    <col min="6" max="6" width="16.3362831858407" style="33"/>
     <col min="7" max="7" width="15.2212389380531" customWidth="1"/>
     <col min="8" max="8" width="23.3362831858407" customWidth="1"/>
     <col min="9" max="9" width="16.1061946902655" customWidth="1"/>
@@ -3109,868 +3349,868 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="35" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" ht="13.85" spans="1:10">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="38" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28" t="s">
+      <c r="E3" s="35"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="35">
         <v>3.5</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28" t="s">
+      <c r="E4" s="35"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28" t="s">
+      <c r="E5" s="35"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28" t="s">
+      <c r="E6" s="35"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="35">
         <v>3</v>
       </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28" t="s">
+      <c r="E7" s="35"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="35">
         <v>4</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28" t="s">
+      <c r="E8" s="35"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="35">
         <v>3.5</v>
       </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28" t="s">
+      <c r="E9" s="35"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28" t="s">
+      <c r="E10" s="35"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28" t="s">
+      <c r="E11" s="35"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="35">
         <v>3</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28" t="s">
+      <c r="E12" s="35"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28" t="s">
+      <c r="E13" s="35"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28" t="s">
+      <c r="E14" s="35"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28" t="s">
+      <c r="E15" s="35"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28" t="s">
+      <c r="E16" s="35"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="35">
         <v>0</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28" t="s">
+      <c r="E17" s="35"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28" t="s">
+      <c r="E18" s="35"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="35">
         <v>5</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28" t="s">
+      <c r="E19" s="35"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="35">
         <v>0</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28" t="s">
+      <c r="E20" s="35"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28" t="s">
+      <c r="E21" s="35"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="35">
         <v>0</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="35">
         <v>0</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="35">
         <v>0</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28" t="s">
+      <c r="E22" s="35"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="35">
         <v>0</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28" t="s">
+      <c r="E23" s="35"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28" t="s">
+      <c r="E24" s="35"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28" t="s">
+      <c r="E25" s="35"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28" t="s">
+      <c r="E26" s="35"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28" t="s">
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28" t="s">
+      <c r="E28" s="35"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="35">
         <v>3</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28" t="s">
+      <c r="E29" s="35"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="35">
         <v>3</v>
       </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28" t="s">
+      <c r="E30" s="35"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28" t="s">
+      <c r="E31" s="35"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="35">
         <v>3</v>
       </c>
-      <c r="E32" s="28"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28" t="s">
+      <c r="E32" s="35"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="34"/>
+      <c r="A35" s="41"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="34"/>
+      <c r="A36" s="41"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="34"/>
+      <c r="A37" s="41"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="34"/>
+      <c r="A38" s="41"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="34"/>
+      <c r="A39" s="41"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="34"/>
+      <c r="A40" s="41"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="34"/>
+      <c r="A41" s="41"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="34"/>
+      <c r="A42" s="41"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="34"/>
+      <c r="A43" s="41"/>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="34"/>
+      <c r="A44" s="41"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="34"/>
+      <c r="A45" s="41"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="34"/>
-      <c r="F46" s="35"/>
+      <c r="A46" s="41"/>
+      <c r="F46" s="42"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="34"/>
-      <c r="F47" s="35"/>
+      <c r="A47" s="41"/>
+      <c r="F47" s="42"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="34"/>
-      <c r="F48" s="35"/>
+      <c r="A48" s="41"/>
+      <c r="F48" s="42"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="34"/>
-      <c r="F49" s="35"/>
+      <c r="A49" s="41"/>
+      <c r="F49" s="42"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="34"/>
-      <c r="F50" s="35"/>
+      <c r="A50" s="41"/>
+      <c r="F50" s="42"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="34"/>
-      <c r="F51" s="35"/>
+      <c r="A51" s="41"/>
+      <c r="F51" s="42"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="34"/>
-      <c r="F52" s="35"/>
+      <c r="A52" s="41"/>
+      <c r="F52" s="42"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="34"/>
-      <c r="F53" s="35"/>
+      <c r="A53" s="41"/>
+      <c r="F53" s="42"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="34"/>
-      <c r="F54" s="35"/>
+      <c r="A54" s="41"/>
+      <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="34"/>
-      <c r="F55" s="35"/>
+      <c r="A55" s="41"/>
+      <c r="F55" s="42"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="34"/>
-      <c r="F56" s="35"/>
+      <c r="A56" s="41"/>
+      <c r="F56" s="42"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="34"/>
-      <c r="F57" s="35"/>
+      <c r="A57" s="41"/>
+      <c r="F57" s="42"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="34"/>
-      <c r="F58" s="35"/>
+      <c r="A58" s="41"/>
+      <c r="F58" s="42"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="34"/>
-      <c r="F59" s="35"/>
+      <c r="A59" s="41"/>
+      <c r="F59" s="42"/>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="34"/>
-      <c r="F60" s="35"/>
+      <c r="A60" s="41"/>
+      <c r="F60" s="42"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="34"/>
-      <c r="F61" s="35"/>
+      <c r="A61" s="41"/>
+      <c r="F61" s="42"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="34"/>
-      <c r="F62" s="35"/>
+      <c r="A62" s="41"/>
+      <c r="F62" s="42"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="34"/>
-      <c r="F63" s="35"/>
+      <c r="A63" s="41"/>
+      <c r="F63" s="42"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="34"/>
-      <c r="F64" s="35"/>
+      <c r="A64" s="41"/>
+      <c r="F64" s="42"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="34"/>
-      <c r="F65" s="35"/>
+      <c r="A65" s="41"/>
+      <c r="F65" s="42"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="34"/>
-      <c r="F66" s="35"/>
+      <c r="A66" s="41"/>
+      <c r="F66" s="42"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="34"/>
-      <c r="F67" s="35"/>
+      <c r="A67" s="41"/>
+      <c r="F67" s="42"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="34"/>
-      <c r="F68" s="35"/>
+      <c r="A68" s="41"/>
+      <c r="F68" s="42"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="34"/>
-      <c r="F69" s="35"/>
+      <c r="A69" s="41"/>
+      <c r="F69" s="42"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="34"/>
-      <c r="F70" s="35"/>
+      <c r="A70" s="41"/>
+      <c r="F70" s="42"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="34"/>
-      <c r="F71" s="35"/>
+      <c r="A71" s="41"/>
+      <c r="F71" s="42"/>
     </row>
     <row r="72" spans="6:6">
-      <c r="F72" s="35"/>
+      <c r="F72" s="42"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B2:J32" etc:filterBottomFollowUsedRange="0">
@@ -4017,785 +4257,785 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="12.35" spans="1:8">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="10.95" customHeight="1" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" s="11" customFormat="1" ht="24.75" spans="1:21">
-      <c r="A4" s="12">
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" s="18" customFormat="1" ht="24.75" spans="1:21">
+      <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="20">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="21">
         <v>3</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="20" t="s">
         <v>103</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-    </row>
-    <row r="5" s="3" customFormat="1" ht="24.75" spans="1:12">
-      <c r="A5" s="15">
+      <c r="K4" s="11"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+    </row>
+    <row r="5" s="11" customFormat="1" ht="24.75" spans="1:12">
+      <c r="A5" s="22">
         <v>2</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="23">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="24">
         <v>3</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="23" t="s">
         <v>107</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="L5" s="23"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" ht="37.15" spans="1:8">
-      <c r="A6" s="18">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="26">
         <v>3</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="26">
         <v>3</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="26" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" ht="37.15" spans="1:8">
-      <c r="A7" s="15">
+      <c r="A7" s="22">
         <v>4</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="23">
         <v>4</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="24">
         <v>3</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="23" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" ht="24.75" spans="1:8">
-      <c r="A8" s="18">
+      <c r="A8" s="25">
         <v>5</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="26">
         <v>5</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="27">
         <v>3</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="26" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="9" ht="37.15" spans="1:8">
-      <c r="A9" s="15">
+      <c r="A9" s="22">
         <v>6</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="23">
         <v>6</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="23">
         <v>3</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="23" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" ht="37.15" spans="1:8">
-      <c r="A10" s="18">
+      <c r="A10" s="25">
         <v>7</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="26">
         <v>7</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="27">
         <v>3</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="26" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" ht="37.15" spans="1:8">
-      <c r="A11" s="15">
+      <c r="A11" s="22">
         <v>8</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="23">
         <v>8</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="24">
         <v>3</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" ht="37.15" spans="1:8">
-      <c r="A12" s="18">
+      <c r="A12" s="25">
         <v>9</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="26">
         <v>9</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="26">
         <v>5</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="26" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="13" ht="37.15" spans="1:8">
-      <c r="A13" s="15">
+      <c r="A13" s="22">
         <v>10</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="23">
         <v>10</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="24">
         <v>3</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="23" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="14" ht="24.75" spans="1:8">
-      <c r="A14" s="18">
+      <c r="A14" s="25">
         <v>11</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="26">
         <v>11</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="27">
         <v>1</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="26" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="15">
+      <c r="A15" s="22">
         <v>12</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="23">
         <v>12</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="18">
+      <c r="A16" s="25">
         <v>13</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="26">
         <v>13</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="15">
+      <c r="A17" s="22">
         <v>14</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="23">
         <v>14</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="18">
+      <c r="A18" s="25">
         <v>15</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="26">
         <v>15</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="15">
+      <c r="A19" s="22">
         <v>16</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="23">
         <v>16</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="18">
+      <c r="A20" s="25">
         <v>17</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="26">
         <v>17</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="15">
+      <c r="A21" s="22">
         <v>18</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="23">
         <v>18</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="18">
+      <c r="A22" s="25">
         <v>19</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="26">
         <v>19</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="15">
+      <c r="A23" s="22">
         <v>20</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="23">
         <v>20</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="18">
+      <c r="A24" s="25">
         <v>21</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="26">
         <v>21</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="15">
+      <c r="A25" s="22">
         <v>22</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="23">
         <v>22</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="18">
+      <c r="A26" s="25">
         <v>23</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="26">
         <v>23</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="15">
+      <c r="A27" s="22">
         <v>24</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="23">
         <v>24</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" ht="37.15" spans="1:8">
-      <c r="A28" s="18">
+      <c r="A28" s="25">
         <v>25</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="26">
         <v>25</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="27">
         <v>3</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="26" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="15">
+      <c r="A29" s="22">
         <v>26</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="23">
         <v>26</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="18">
+      <c r="A30" s="25">
         <v>27</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="26">
         <v>27</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="15">
+      <c r="A31" s="22">
         <v>28</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="23">
         <v>28</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="18">
+      <c r="A32" s="25">
         <v>29</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="26">
         <v>29</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="15">
+      <c r="A33" s="22">
         <v>30</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="23">
         <v>30</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="11">
+      <c r="A34" s="18">
         <v>31</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="18">
         <v>31</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="3">
+      <c r="A35" s="11">
         <v>32</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="11">
         <v>32</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="4"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="11">
+      <c r="A36" s="18">
         <v>33</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="18">
         <v>33</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="3">
+      <c r="A37" s="11">
         <v>34</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="11">
         <v>34</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="4"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="2"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="11">
+      <c r="A38" s="18">
         <v>35</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="18">
         <v>35</v>
       </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="3">
+      <c r="A39" s="11">
         <v>36</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="11">
         <v>36</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="4"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="11">
+      <c r="A40" s="18">
         <v>37</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="18">
         <v>37</v>
       </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="3">
+      <c r="A41" s="11">
         <v>38</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="11">
         <v>38</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="4"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="2"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="11">
+      <c r="A42" s="18">
         <v>39</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="18">
         <v>39</v>
       </c>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="3">
+      <c r="A43" s="11">
         <v>40</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="11">
         <v>40</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="4"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
     </row>
     <row r="45" spans="5:5">
-      <c r="E45" s="16"/>
+      <c r="E45" s="23"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G45" etc:filterBottomFollowUsedRange="0">
@@ -4831,17 +5071,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -4876,26 +5105,26 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="12.4" spans="1:11">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>146</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -4909,391 +5138,1486 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="12.4" spans="1:12">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="13" t="s">
         <v>154</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="24.75" spans="1:11">
-      <c r="A4" s="2">
+    <row r="4" s="10" customFormat="1" ht="24.75" spans="1:11">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="10">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="10">
         <v>60</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="10">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="10">
         <v>0.02</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="10">
         <v>5</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="37.15" spans="1:11">
-      <c r="A5" s="2">
+    <row r="5" s="10" customFormat="1" ht="37.15" spans="1:11">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="10">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="10">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="10">
         <v>60</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="10">
         <v>1</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="10">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="10">
         <v>20</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="12.35" spans="11:11">
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" s="3" customFormat="1" ht="12.35" spans="11:11">
-      <c r="K7" s="10"/>
+    <row r="6" s="11" customFormat="1" ht="12.35" spans="11:11">
+      <c r="K6" s="17"/>
+    </row>
+    <row r="7" s="11" customFormat="1" ht="12.35" spans="11:11">
+      <c r="K7" s="17"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="K8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="2"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="4"/>
-      <c r="K9" s="10"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="2"/>
+      <c r="K9" s="17"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="K10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="2"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="K11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="2"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
-      <c r="K12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="2"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
-      <c r="K13" s="10"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="2"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
-      <c r="K14" s="10"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="2"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
-      <c r="K15" s="10"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="2"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="4"/>
-      <c r="K16" s="10"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="2"/>
+      <c r="K16" s="17"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
-      <c r="K17" s="10"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="2"/>
+      <c r="K17" s="17"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
-      <c r="K18" s="10"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="2"/>
+      <c r="K18" s="17"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
-      <c r="K19" s="10"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="2"/>
+      <c r="K19" s="17"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
-      <c r="K20" s="10"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="2"/>
+      <c r="K20" s="17"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="12.35" spans="1:11">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="4"/>
-      <c r="K21" s="10"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="2"/>
+      <c r="K21" s="17"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="2"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="4"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="4"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="4"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="4"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="4"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="4"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="2"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="4"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="2"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="4"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="4"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="4"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="2"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="4"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="4"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="4"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="12.35" spans="1:5">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="4"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" ht="24.75" spans="1:7">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="9">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="9">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
+        <v>6</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="9">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="9">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="9">
+        <v>12</v>
+      </c>
+      <c r="B15" s="9">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7">
+        <v>13</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="9">
+        <v>14</v>
+      </c>
+      <c r="B17" s="9">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="7">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7">
+        <v>15</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="8">
+        <v>2</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="9">
+        <v>16</v>
+      </c>
+      <c r="B19" s="9">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7">
+        <v>17</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" s="8">
+        <v>2</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="9">
+        <v>18</v>
+      </c>
+      <c r="B21" s="9">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="7">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7">
+        <v>19</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="8">
+        <v>2</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="9">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="7">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7">
+        <v>21</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="8">
+        <v>3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="9">
+        <v>22</v>
+      </c>
+      <c r="B25" s="9">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>193</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="7">
+        <v>23</v>
+      </c>
+      <c r="B26" s="7">
+        <v>23</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" s="8">
+        <v>3</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="9">
+        <v>24</v>
+      </c>
+      <c r="B27" s="9">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="7">
+        <v>25</v>
+      </c>
+      <c r="B28" s="7">
+        <v>25</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="8">
+        <v>3</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="9">
+        <v>26</v>
+      </c>
+      <c r="B29" s="9">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="7">
+        <v>27</v>
+      </c>
+      <c r="B30" s="7">
+        <v>27</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="8">
+        <v>4</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="9">
+        <v>28</v>
+      </c>
+      <c r="B31" s="9">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="7">
+        <v>29</v>
+      </c>
+      <c r="B32" s="7">
+        <v>29</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="8">
+        <v>4</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="9">
+        <v>30</v>
+      </c>
+      <c r="B33" s="9">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="7">
+        <v>31</v>
+      </c>
+      <c r="B34" s="7">
+        <v>31</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="8">
+        <v>4</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="9">
+        <v>32</v>
+      </c>
+      <c r="B35" s="9">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>203</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="7">
+        <v>33</v>
+      </c>
+      <c r="B36" s="7">
+        <v>33</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D36" s="8">
+        <v>5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="9">
+        <v>34</v>
+      </c>
+      <c r="B37" s="9">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>205</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="7">
+        <v>35</v>
+      </c>
+      <c r="B38" s="7">
+        <v>35</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="8">
+        <v>5</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2</v>
+      </c>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="9">
+        <v>36</v>
+      </c>
+      <c r="B39" s="9">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>207</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="7">
+        <v>37</v>
+      </c>
+      <c r="B40" s="7">
+        <v>37</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D40" s="8">
+        <v>5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="9">
+        <v>38</v>
+      </c>
+      <c r="B41" s="9">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>209</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="7">
+        <v>39</v>
+      </c>
+      <c r="B42" s="7">
+        <v>39</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" s="8">
+        <v>6</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="9">
+        <v>40</v>
+      </c>
+      <c r="B43" s="9">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>211</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="7">
+        <v>41</v>
+      </c>
+      <c r="B44" s="7">
+        <v>41</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" s="8">
+        <v>6</v>
+      </c>
+      <c r="E44" s="8">
+        <v>2</v>
+      </c>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="9">
+        <v>42</v>
+      </c>
+      <c r="B45" s="9">
+        <v>42</v>
+      </c>
+      <c r="C45" t="s">
+        <v>213</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="7">
+        <v>43</v>
+      </c>
+      <c r="B46" s="7">
+        <v>43</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D46" s="8">
+        <v>6</v>
+      </c>
+      <c r="E46" s="8">
+        <v>3</v>
+      </c>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="9">
+        <v>44</v>
+      </c>
+      <c r="B47" s="9">
+        <v>44</v>
+      </c>
+      <c r="C47" t="s">
+        <v>215</v>
+      </c>
+      <c r="D47">
+        <v>7</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="7">
+        <v>45</v>
+      </c>
+      <c r="B48" s="7">
+        <v>45</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48" s="8">
+        <v>7</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="9">
+        <v>46</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46</v>
+      </c>
+      <c r="C49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49">
+        <v>7</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="7">
+        <v>47</v>
+      </c>
+      <c r="B50" s="7">
+        <v>47</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D50" s="8">
+        <v>7</v>
+      </c>
+      <c r="E50" s="8">
+        <v>2</v>
+      </c>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="9">
+        <v>48</v>
+      </c>
+      <c r="B51" s="9">
+        <v>48</v>
+      </c>
+      <c r="C51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51">
+        <v>7</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="7">
+        <v>49</v>
+      </c>
+      <c r="B52" s="7">
+        <v>49</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D52" s="8">
+        <v>7</v>
+      </c>
+      <c r="E52" s="8">
+        <v>3</v>
+      </c>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="9">
+        <v>50</v>
+      </c>
+      <c r="B53" s="9">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>221</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="7">
+        <v>51</v>
+      </c>
+      <c r="B54" s="7">
+        <v>51</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D54" s="8">
+        <v>8</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="9">
+        <v>52</v>
+      </c>
+      <c r="B55" s="9">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>223</v>
+      </c>
+      <c r="D55">
+        <v>8</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="7">
+        <v>53</v>
+      </c>
+      <c r="B56" s="7">
+        <v>53</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D56" s="8">
+        <v>8</v>
+      </c>
+      <c r="E56" s="8">
+        <v>2</v>
+      </c>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="9">
+        <v>54</v>
+      </c>
+      <c r="B57" s="9">
+        <v>54</v>
+      </c>
+      <c r="C57" t="s">
+        <v>225</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="7">
+        <v>55</v>
+      </c>
+      <c r="B58" s="7">
+        <v>55</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D58" s="8">
+        <v>8</v>
+      </c>
+      <c r="E58" s="8">
+        <v>3</v>
+      </c>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
